--- a/S62aMigration/csv_and_xlsx_files/S62A_Column_mapping_for_TEMPLATE.xlsx
+++ b/S62aMigration/csv_and_xlsx_files/S62A_Column_mapping_for_TEMPLATE.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nisalihalwathura/PINS/S62A migration/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nisalihalwathura/PINS/ODW-Service/odw-synapse-workspace/S62aMigration/csv_and_xlsx_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5D753956-51FC-4E41-A5E4-79A7B2B07BDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B933EF4-9E85-3644-9DB2-34042C52231C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3900" yWindow="660" windowWidth="18880" windowHeight="14860" xr2:uid="{12241D67-8D82-4829-AFAA-E70F395389D3}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="19720" xr2:uid="{12241D67-8D82-4829-AFAA-E70F395389D3}"/>
   </bookViews>
   <sheets>
     <sheet name="Lookup" sheetId="5" r:id="rId1"/>
@@ -20,7 +20,7 @@
     <sheet name="Sheet1" sheetId="6" state="hidden" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Lookup!$A$1:$I$206</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Lookup!$A$1:$I$202</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Sheet3!$A$1:$F$206</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
@@ -58,7 +58,7 @@
     <author>tc={3FD1DC5D-AC6A-441A-9E86-C8CAB64E4AE3}</author>
   </authors>
   <commentList>
-    <comment ref="H47" authorId="0" shapeId="0" xr:uid="{5944ABFF-9804-4CA5-BD49-6FD1AD67BDE0}">
+    <comment ref="H46" authorId="0" shapeId="0" xr:uid="{5944ABFF-9804-4CA5-BD49-6FD1AD67BDE0}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -66,7 +66,7 @@
     Sorry, this should be case_involvement_o as for these cases LPA is always in the o table</t>
       </text>
     </comment>
-    <comment ref="J47" authorId="1" shapeId="0" xr:uid="{C4EEFDE2-0CB2-442D-9C5B-7ACEE508BD1C}">
+    <comment ref="J46" authorId="1" shapeId="0" xr:uid="{C4EEFDE2-0CB2-442D-9C5B-7ACEE508BD1C}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -74,7 +74,7 @@
     New case_involvement file combines personal and organisation data so we don't have two separate files for this entity</t>
       </text>
     </comment>
-    <comment ref="H48" authorId="2" shapeId="0" xr:uid="{80193FFF-BF4E-44D3-9C11-0A4FE76B577A}">
+    <comment ref="H47" authorId="2" shapeId="0" xr:uid="{80193FFF-BF4E-44D3-9C11-0A4FE76B577A}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -82,7 +82,7 @@
     Leave as blank as organisation name can be put as first name</t>
       </text>
     </comment>
-    <comment ref="J49" authorId="3" shapeId="0" xr:uid="{B92225D1-91C3-4EF9-8E4F-93882A077335}">
+    <comment ref="J48" authorId="3" shapeId="0" xr:uid="{B92225D1-91C3-4EF9-8E4F-93882A077335}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -90,7 +90,7 @@
     SQL extract already includes this logic so we don't have to implement this as part of the script</t>
       </text>
     </comment>
-    <comment ref="H68" authorId="4" shapeId="0" xr:uid="{017BB77F-CAB8-407F-ACBF-0DEF9EBD8425}">
+    <comment ref="H67" authorId="4" shapeId="0" xr:uid="{017BB77F-CAB8-407F-ACBF-0DEF9EBD8425}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -98,7 +98,7 @@
     Should be case_involvement_o.Address1 etc if Applicant for that case is in the case_involvement_o table, and case_involvement_p.Address1 etc if the Applicant for that case is in the case_involvement_p table (see case_involvement tab of this spreadsheet)</t>
       </text>
     </comment>
-    <comment ref="H83" authorId="5" shapeId="0" xr:uid="{9C81533C-1346-4746-BA46-4A0884AA6955}">
+    <comment ref="H82" authorId="5" shapeId="0" xr:uid="{9C81533C-1346-4746-BA46-4A0884AA6955}">
       <text>
         <t xml:space="preserve">[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -107,7 +107,7 @@
 </t>
       </text>
     </comment>
-    <comment ref="H136" authorId="6" shapeId="0" xr:uid="{3FD1DC5D-AC6A-441A-9E86-C8CAB64E4AE3}">
+    <comment ref="H132" authorId="6" shapeId="0" xr:uid="{3FD1DC5D-AC6A-441A-9E86-C8CAB64E4AE3}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -122,7 +122,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3348" uniqueCount="507">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3317" uniqueCount="508">
   <si>
     <t>Template LEGACY cases S62A</t>
   </si>
@@ -1643,6 +1643,9 @@
   </si>
   <si>
     <t>same as LPA code</t>
+  </si>
+  <si>
+    <t>case_involvement.Postcode</t>
   </si>
 </sst>
 </file>
@@ -2106,29 +2109,29 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="H47" dT="2026-09-02T09:08:20.85" personId="{89F31B65-721C-4DD4-A1C6-0FC00A173227}" id="{5944ABFF-9804-4CA5-BD49-6FD1AD67BDE0}">
+  <threadedComment ref="H46" dT="2026-09-02T09:08:20.85" personId="{89F31B65-721C-4DD4-A1C6-0FC00A173227}" id="{5944ABFF-9804-4CA5-BD49-6FD1AD67BDE0}">
     <text>Sorry, this should be case_involvement_o as for these cases LPA is always in the o table</text>
   </threadedComment>
-  <threadedComment ref="J47" dT="2026-09-03T10:36:29.47" personId="{15D4F506-EB10-435F-84F5-95037BE0C4BF}" id="{C4EEFDE2-0CB2-442D-9C5B-7ACEE508BD1C}">
+  <threadedComment ref="J46" dT="2026-09-03T10:36:29.47" personId="{15D4F506-EB10-435F-84F5-95037BE0C4BF}" id="{C4EEFDE2-0CB2-442D-9C5B-7ACEE508BD1C}">
     <text>New case_involvement file combines personal and organisation data so we don't have two separate files for this entity</text>
   </threadedComment>
-  <threadedComment ref="H48" dT="2026-09-03T10:14:46.55" personId="{15D4F506-EB10-435F-84F5-95037BE0C4BF}" id="{80193FFF-BF4E-44D3-9C11-0A4FE76B577A}">
+  <threadedComment ref="H47" dT="2026-09-03T10:14:46.55" personId="{15D4F506-EB10-435F-84F5-95037BE0C4BF}" id="{80193FFF-BF4E-44D3-9C11-0A4FE76B577A}">
     <text>Leave as blank as organisation name can be put as first name</text>
   </threadedComment>
-  <threadedComment ref="J49" dT="2026-09-03T10:35:49.72" personId="{15D4F506-EB10-435F-84F5-95037BE0C4BF}" id="{B92225D1-91C3-4EF9-8E4F-93882A077335}">
+  <threadedComment ref="J48" dT="2026-09-03T10:35:49.72" personId="{15D4F506-EB10-435F-84F5-95037BE0C4BF}" id="{B92225D1-91C3-4EF9-8E4F-93882A077335}">
     <text>SQL extract already includes this logic so we don't have to implement this as part of the script</text>
   </threadedComment>
-  <threadedComment ref="H68" dT="2026-09-02T09:07:15.83" personId="{89F31B65-721C-4DD4-A1C6-0FC00A173227}" id="{017BB77F-CAB8-407F-ACBF-0DEF9EBD8425}">
+  <threadedComment ref="H67" dT="2026-09-02T09:07:15.83" personId="{89F31B65-721C-4DD4-A1C6-0FC00A173227}" id="{017BB77F-CAB8-407F-ACBF-0DEF9EBD8425}">
     <text>Should be case_involvement_o.Address1 etc if Applicant for that case is in the case_involvement_o table, and case_involvement_p.Address1 etc if the Applicant for that case is in the case_involvement_p table (see case_involvement tab of this spreadsheet)</text>
   </threadedComment>
-  <threadedComment ref="H83" dT="2026-09-02T09:08:50.35" personId="{89F31B65-721C-4DD4-A1C6-0FC00A173227}" id="{9C81533C-1346-4746-BA46-4A0884AA6955}">
+  <threadedComment ref="H82" dT="2026-09-02T09:08:50.35" personId="{89F31B65-721C-4DD4-A1C6-0FC00A173227}" id="{9C81533C-1346-4746-BA46-4A0884AA6955}">
     <text xml:space="preserve">o if in o table, p if in p table for the selected case
 </text>
   </threadedComment>
-  <threadedComment ref="H136" dT="2026-09-03T15:49:18.94" personId="{15D4F506-EB10-435F-84F5-95037BE0C4BF}" id="{3FD1DC5D-AC6A-441A-9E86-C8CAB64E4AE3}">
+  <threadedComment ref="H132" dT="2026-09-03T15:49:18.94" personId="{15D4F506-EB10-435F-84F5-95037BE0C4BF}" id="{3FD1DC5D-AC6A-441A-9E86-C8CAB64E4AE3}">
     <text>clarify column where we are pulling from</text>
   </threadedComment>
-  <threadedComment ref="H136" dT="2026-09-03T18:07:05.09" personId="{15D4F506-EB10-435F-84F5-95037BE0C4BF}" id="{42CB06BF-42E5-40F4-9650-512652EA889F}" parentId="{3FD1DC5D-AC6A-441A-9E86-C8CAB64E4AE3}">
+  <threadedComment ref="H132" dT="2026-09-03T18:07:05.09" personId="{15D4F506-EB10-435F-84F5-95037BE0C4BF}" id="{42CB06BF-42E5-40F4-9650-512652EA889F}" parentId="{3FD1DC5D-AC6A-441A-9E86-C8CAB64E4AE3}">
     <text>changed to ApplicationFeeReceivedDate</text>
   </threadedComment>
 </ThreadedComments>
@@ -2747,157 +2750,157 @@
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B24" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C24" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="D24" s="5" t="s">
         <v>16</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="G24" s="8" t="s">
         <v>11</v>
       </c>
       <c r="H24" s="10" t="s">
-        <v>84</v>
-      </c>
-      <c r="I24" s="13"/>
+        <v>16</v>
+      </c>
+      <c r="I24" s="13" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B25" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C25" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D25" s="5" t="s">
         <v>16</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>86</v>
+        <v>16</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="G25" s="8" t="s">
-        <v>11</v>
+        <v>16</v>
+      </c>
+      <c r="G25" s="13" t="s">
+        <v>71</v>
       </c>
       <c r="H25" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="I25" s="13" t="s">
-        <v>31</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="I25" s="13"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B26" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C26" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D26" s="5" t="s">
         <v>16</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>16</v>
+        <v>90</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="G26" s="13" t="s">
-        <v>71</v>
+        <v>90</v>
+      </c>
+      <c r="G26" s="8" t="s">
+        <v>11</v>
       </c>
       <c r="H26" s="10" t="s">
-        <v>88</v>
-      </c>
-      <c r="I26" s="13"/>
+        <v>16</v>
+      </c>
+      <c r="I26" s="13" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B27" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C27" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="D27" s="5" t="s">
         <v>16</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>90</v>
+        <v>16</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="G27" s="8" t="s">
-        <v>11</v>
+        <v>16</v>
+      </c>
+      <c r="G27" s="13" t="s">
+        <v>71</v>
       </c>
       <c r="H27" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="I27" s="13" t="s">
-        <v>31</v>
-      </c>
+        <v>93</v>
+      </c>
+      <c r="I27" s="13"/>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B28" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C28" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D28" s="5" t="s">
         <v>16</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>16</v>
+        <v>95</v>
       </c>
       <c r="F28" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="G28" s="13" t="s">
-        <v>71</v>
+        <v>95</v>
+      </c>
+      <c r="G28" s="8" t="s">
+        <v>11</v>
       </c>
       <c r="H28" s="10" t="s">
-        <v>93</v>
-      </c>
-      <c r="I28" s="13"/>
+        <v>16</v>
+      </c>
+      <c r="I28" s="13" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B29" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C29" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="D29" s="5" t="s">
         <v>16</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="F29" s="5" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="G29" s="8" t="s">
         <v>11</v>
       </c>
       <c r="H29" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="I29" s="13" t="s">
-        <v>31</v>
-      </c>
+        <v>99</v>
+      </c>
+      <c r="I29" s="13"/>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B30" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="C30" t="s">
         <v>97</v>
@@ -2906,46 +2909,48 @@
         <v>16</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="G30" s="8" t="s">
         <v>11</v>
       </c>
       <c r="H30" s="10" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="I30" s="13"/>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B31" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="C31" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="D31" s="5" t="s">
         <v>16</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="F31" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="G31" s="8" t="s">
-        <v>11</v>
+        <v>104</v>
+      </c>
+      <c r="G31" s="13" t="s">
+        <v>105</v>
       </c>
       <c r="H31" s="10" t="s">
-        <v>102</v>
-      </c>
-      <c r="I31" s="13"/>
+        <v>16</v>
+      </c>
+      <c r="I31" s="13" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B32" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="C32" t="s">
         <v>104</v>
@@ -2960,7 +2965,7 @@
         <v>104</v>
       </c>
       <c r="G32" s="13" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="H32" s="10" t="s">
         <v>16</v>
@@ -2971,110 +2976,108 @@
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B33" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C33" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="D33" s="5" t="s">
         <v>16</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="F33" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="G33" s="13" t="s">
-        <v>107</v>
+        <v>109</v>
+      </c>
+      <c r="G33" s="8" t="s">
+        <v>11</v>
       </c>
       <c r="H33" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="I33" s="13" t="s">
-        <v>31</v>
-      </c>
+        <v>110</v>
+      </c>
+      <c r="I33" s="13"/>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B34" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="C34" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="D34" s="5" t="s">
         <v>16</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="F34" s="5" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="G34" s="8" t="s">
         <v>11</v>
       </c>
       <c r="H34" s="10" t="s">
-        <v>110</v>
-      </c>
-      <c r="I34" s="13"/>
+        <v>16</v>
+      </c>
+      <c r="I34" s="13" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B35" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C35" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D35" s="5" t="s">
         <v>16</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="F35" s="5" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="G35" s="8" t="s">
         <v>11</v>
       </c>
       <c r="H35" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="I35" s="13" t="s">
-        <v>31</v>
-      </c>
+        <v>115</v>
+      </c>
+      <c r="I35" s="13"/>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B36" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="C36" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="D36" s="5" t="s">
         <v>16</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>113</v>
+        <v>16</v>
       </c>
       <c r="F36" s="5" t="s">
-        <v>114</v>
+        <v>16</v>
       </c>
       <c r="G36" s="8" t="s">
         <v>11</v>
       </c>
       <c r="H36" s="10" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="I36" s="13"/>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B37" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C37" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D37" s="5" t="s">
         <v>16</v>
@@ -3089,42 +3092,44 @@
         <v>11</v>
       </c>
       <c r="H37" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="I37" s="13"/>
+        <v>16</v>
+      </c>
+      <c r="I37" s="13" t="s">
+        <v>119</v>
+      </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B38" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C38" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>16</v>
+        <v>121</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>16</v>
+        <v>122</v>
       </c>
       <c r="F38" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="G38" s="8" t="s">
-        <v>11</v>
+        <v>122</v>
+      </c>
+      <c r="G38" s="13" t="s">
+        <v>123</v>
       </c>
       <c r="H38" s="10" t="s">
         <v>16</v>
       </c>
       <c r="I38" s="13" t="s">
-        <v>119</v>
+        <v>31</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B39" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="C39" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="D39" s="5" t="s">
         <v>121</v>
@@ -3136,7 +3141,7 @@
         <v>122</v>
       </c>
       <c r="G39" s="13" t="s">
-        <v>123</v>
+        <v>80</v>
       </c>
       <c r="H39" s="10" t="s">
         <v>16</v>
@@ -3146,40 +3151,40 @@
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A40" t="s">
+        <v>126</v>
+      </c>
       <c r="B40" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="C40" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>121</v>
+        <v>16</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>122</v>
+        <v>16</v>
       </c>
       <c r="F40" s="5" t="s">
-        <v>122</v>
+        <v>16</v>
       </c>
       <c r="G40" s="13" t="s">
-        <v>80</v>
+        <v>128</v>
       </c>
       <c r="H40" s="10" t="s">
         <v>16</v>
       </c>
       <c r="I40" s="13" t="s">
-        <v>31</v>
+        <v>128</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A41" t="s">
-        <v>126</v>
-      </c>
       <c r="B41" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C41" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D41" s="5" t="s">
         <v>16</v>
@@ -3201,76 +3206,76 @@
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A42" t="s">
+        <v>130</v>
+      </c>
       <c r="B42" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C42" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="D42" s="5" t="s">
         <v>16</v>
       </c>
       <c r="E42" s="5" t="s">
-        <v>16</v>
+        <v>133</v>
       </c>
       <c r="F42" s="5" t="s">
-        <v>16</v>
+        <v>133</v>
       </c>
       <c r="G42" s="13" t="s">
         <v>128</v>
       </c>
       <c r="H42" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="I42" s="13" t="s">
-        <v>128</v>
-      </c>
+        <v>134</v>
+      </c>
+      <c r="I42" s="13"/>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A43" t="s">
-        <v>130</v>
-      </c>
       <c r="B43" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="C43" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>16</v>
+        <v>46</v>
       </c>
       <c r="E43" s="5" t="s">
-        <v>133</v>
+        <v>16</v>
       </c>
       <c r="F43" s="5" t="s">
-        <v>133</v>
+        <v>16</v>
       </c>
       <c r="G43" s="13" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="H43" s="10" t="s">
-        <v>134</v>
-      </c>
-      <c r="I43" s="13"/>
+        <v>16</v>
+      </c>
+      <c r="I43" s="13" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B44" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="C44" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="D44" s="5" t="s">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="E44" s="5" t="s">
-        <v>16</v>
+        <v>139</v>
       </c>
       <c r="F44" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="G44" s="13" t="s">
-        <v>137</v>
+        <v>139</v>
+      </c>
+      <c r="G44" s="8" t="s">
+        <v>11</v>
       </c>
       <c r="H44" s="10" t="s">
         <v>16</v>
@@ -3280,61 +3285,64 @@
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A45" t="s">
+        <v>140</v>
+      </c>
       <c r="B45" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C45" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>10</v>
+        <v>140</v>
       </c>
       <c r="E45" s="5" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F45" s="5" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="G45" s="8" t="s">
         <v>11</v>
       </c>
       <c r="H45" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="I45" s="13" t="s">
-        <v>31</v>
-      </c>
+        <v>142</v>
+      </c>
+      <c r="I45" s="13"/>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A46" t="s">
-        <v>140</v>
-      </c>
       <c r="B46" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="C46" t="s">
         <v>141</v>
       </c>
       <c r="D46" s="5" t="s">
-        <v>140</v>
+        <v>16</v>
       </c>
       <c r="E46" s="5" t="s">
-        <v>140</v>
+        <v>16</v>
       </c>
       <c r="F46" s="5" t="s">
-        <v>140</v>
+        <v>16</v>
       </c>
       <c r="G46" s="8" t="s">
         <v>11</v>
       </c>
       <c r="H46" s="10" t="s">
-        <v>142</v>
-      </c>
-      <c r="I46" s="13"/>
+        <v>144</v>
+      </c>
+      <c r="I46" s="14" t="s">
+        <v>145</v>
+      </c>
+      <c r="J46" t="s">
+        <v>146</v>
+      </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B47" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="C47" t="s">
         <v>141</v>
@@ -3352,18 +3360,16 @@
         <v>11</v>
       </c>
       <c r="H47" s="10" t="s">
-        <v>144</v>
-      </c>
-      <c r="I47" s="14" t="s">
-        <v>145</v>
-      </c>
-      <c r="J47" t="s">
-        <v>146</v>
+        <v>16</v>
+      </c>
+      <c r="I47" s="14"/>
+      <c r="J47" s="10" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B48" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C48" t="s">
         <v>141</v>
@@ -3380,17 +3386,19 @@
       <c r="G48" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="H48" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="I48" s="14"/>
-      <c r="J48" s="10" t="s">
-        <v>148</v>
+      <c r="H48" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="I48" s="14" t="s">
+        <v>151</v>
+      </c>
+      <c r="J48" s="11" t="s">
+        <v>152</v>
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B49" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="C49" t="s">
         <v>141</v>
@@ -3407,22 +3415,25 @@
       <c r="G49" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="H49" s="11" t="s">
-        <v>150</v>
+      <c r="H49" s="10" t="s">
+        <v>154</v>
       </c>
       <c r="I49" s="14" t="s">
         <v>151</v>
       </c>
-      <c r="J49" s="11" t="s">
-        <v>152</v>
+      <c r="J49" s="10" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A50" t="s">
+        <v>155</v>
+      </c>
       <c r="B50" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C50" t="s">
-        <v>141</v>
+        <v>156</v>
       </c>
       <c r="D50" s="5" t="s">
         <v>16</v>
@@ -3437,21 +3448,15 @@
         <v>11</v>
       </c>
       <c r="H50" s="10" t="s">
-        <v>154</v>
-      </c>
-      <c r="I50" s="14" t="s">
-        <v>151</v>
-      </c>
-      <c r="J50" s="10" t="s">
-        <v>154</v>
+        <v>16</v>
+      </c>
+      <c r="I50" s="13" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A51" t="s">
-        <v>155</v>
-      </c>
       <c r="B51" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="C51" t="s">
         <v>156</v>
@@ -3477,7 +3482,7 @@
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B52" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C52" t="s">
         <v>156</v>
@@ -3503,7 +3508,7 @@
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B53" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C53" t="s">
         <v>156</v>
@@ -3529,7 +3534,7 @@
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B54" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C54" t="s">
         <v>156</v>
@@ -3554,55 +3559,55 @@
       </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A55" t="s">
+        <v>162</v>
+      </c>
       <c r="B55" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C55" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="D55" s="5" t="s">
-        <v>16</v>
+        <v>162</v>
       </c>
       <c r="E55" s="5" t="s">
-        <v>16</v>
+        <v>162</v>
       </c>
       <c r="F55" s="5" t="s">
-        <v>16</v>
+        <v>162</v>
       </c>
       <c r="G55" s="8" t="s">
         <v>11</v>
       </c>
       <c r="H55" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="I55" s="13" t="s">
-        <v>157</v>
+        <v>144</v>
+      </c>
+      <c r="I55" s="14" t="s">
+        <v>164</v>
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A56" t="s">
-        <v>162</v>
-      </c>
       <c r="B56" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C56" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="D56" s="5" t="s">
-        <v>162</v>
+        <v>16</v>
       </c>
       <c r="E56" s="5" t="s">
-        <v>162</v>
+        <v>16</v>
       </c>
       <c r="F56" s="5" t="s">
-        <v>162</v>
-      </c>
-      <c r="G56" s="8" t="s">
-        <v>11</v>
+        <v>16</v>
+      </c>
+      <c r="G56" s="13" t="s">
+        <v>167</v>
       </c>
       <c r="H56" s="10" t="s">
-        <v>144</v>
+        <v>168</v>
       </c>
       <c r="I56" s="14" t="s">
         <v>164</v>
@@ -3610,7 +3615,7 @@
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B57" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="C57" t="s">
         <v>166</v>
@@ -3628,7 +3633,7 @@
         <v>167</v>
       </c>
       <c r="H57" s="10" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="I57" s="14" t="s">
         <v>164</v>
@@ -3636,7 +3641,7 @@
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B58" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C58" t="s">
         <v>166</v>
@@ -3654,7 +3659,7 @@
         <v>167</v>
       </c>
       <c r="H58" s="10" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="I58" s="14" t="s">
         <v>164</v>
@@ -3662,7 +3667,7 @@
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B59" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C59" t="s">
         <v>166</v>
@@ -3680,7 +3685,7 @@
         <v>167</v>
       </c>
       <c r="H59" s="10" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="I59" s="14" t="s">
         <v>164</v>
@@ -3688,7 +3693,7 @@
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B60" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C60" t="s">
         <v>166</v>
@@ -3706,7 +3711,7 @@
         <v>167</v>
       </c>
       <c r="H60" s="10" t="s">
-        <v>174</v>
+        <v>507</v>
       </c>
       <c r="I60" s="14" t="s">
         <v>164</v>
@@ -3714,7 +3719,7 @@
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B61" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="C61" t="s">
         <v>166</v>
@@ -3732,7 +3737,7 @@
         <v>167</v>
       </c>
       <c r="H61" s="10" t="s">
-        <v>176</v>
+        <v>146</v>
       </c>
       <c r="I61" s="14" t="s">
         <v>164</v>
@@ -3740,7 +3745,7 @@
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B62" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C62" t="s">
         <v>166</v>
@@ -3758,7 +3763,7 @@
         <v>167</v>
       </c>
       <c r="H62" s="10" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="I62" s="14" t="s">
         <v>164</v>
@@ -3766,7 +3771,7 @@
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B63" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C63" t="s">
         <v>166</v>
@@ -3784,7 +3789,7 @@
         <v>167</v>
       </c>
       <c r="H63" s="10" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="I63" s="14" t="s">
         <v>164</v>
@@ -3792,7 +3797,7 @@
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B64" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C64" t="s">
         <v>166</v>
@@ -3809,19 +3814,22 @@
       <c r="G64" s="13" t="s">
         <v>167</v>
       </c>
-      <c r="H64" s="10" t="s">
-        <v>154</v>
+      <c r="H64" s="11" t="s">
+        <v>150</v>
       </c>
       <c r="I64" s="14" t="s">
-        <v>164</v>
+        <v>181</v>
       </c>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A65" t="s">
+        <v>182</v>
+      </c>
       <c r="B65" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="C65" t="s">
-        <v>166</v>
+        <v>183</v>
       </c>
       <c r="D65" s="5" t="s">
         <v>16</v>
@@ -3833,73 +3841,70 @@
         <v>16</v>
       </c>
       <c r="G65" s="13" t="s">
-        <v>167</v>
-      </c>
-      <c r="H65" s="11" t="s">
-        <v>150</v>
-      </c>
-      <c r="I65" s="14" t="s">
-        <v>181</v>
+        <v>184</v>
+      </c>
+      <c r="H65" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="I65" s="13" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A66" t="s">
+      <c r="B66" t="s">
+        <v>185</v>
+      </c>
+      <c r="C66" t="s">
+        <v>185</v>
+      </c>
+      <c r="D66" s="5" t="s">
         <v>182</v>
       </c>
-      <c r="B66" t="s">
-        <v>183</v>
-      </c>
-      <c r="C66" t="s">
-        <v>183</v>
-      </c>
-      <c r="D66" s="5" t="s">
-        <v>16</v>
-      </c>
       <c r="E66" s="5" t="s">
-        <v>16</v>
+        <v>182</v>
       </c>
       <c r="F66" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="G66" s="13" t="s">
-        <v>184</v>
+        <v>182</v>
+      </c>
+      <c r="G66" s="8" t="s">
+        <v>11</v>
       </c>
       <c r="H66" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="I66" s="13" t="s">
-        <v>128</v>
+        <v>186</v>
+      </c>
+      <c r="I66" s="8" t="s">
+        <v>187</v>
       </c>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B67" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="C67" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="D67" s="5" t="s">
-        <v>182</v>
+        <v>16</v>
       </c>
       <c r="E67" s="5" t="s">
-        <v>182</v>
+        <v>16</v>
       </c>
       <c r="F67" s="5" t="s">
-        <v>182</v>
-      </c>
-      <c r="G67" s="8" t="s">
-        <v>11</v>
+        <v>16</v>
+      </c>
+      <c r="G67" s="13" t="s">
+        <v>190</v>
       </c>
       <c r="H67" s="10" t="s">
-        <v>186</v>
-      </c>
-      <c r="I67" s="8" t="s">
+        <v>168</v>
+      </c>
+      <c r="I67" s="14" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B68" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="C68" t="s">
         <v>189</v>
@@ -3917,7 +3922,7 @@
         <v>190</v>
       </c>
       <c r="H68" s="10" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="I68" s="14" t="s">
         <v>187</v>
@@ -3925,7 +3930,7 @@
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B69" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C69" t="s">
         <v>189</v>
@@ -3943,15 +3948,15 @@
         <v>190</v>
       </c>
       <c r="H69" s="10" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="I69" s="14" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B70" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C70" t="s">
         <v>189</v>
@@ -3969,7 +3974,7 @@
         <v>190</v>
       </c>
       <c r="H70" s="10" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="I70" s="14" t="s">
         <v>193</v>
@@ -3977,7 +3982,7 @@
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B71" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C71" t="s">
         <v>189</v>
@@ -3995,7 +4000,7 @@
         <v>190</v>
       </c>
       <c r="H71" s="10" t="s">
-        <v>174</v>
+        <v>507</v>
       </c>
       <c r="I71" s="14" t="s">
         <v>193</v>
@@ -4003,7 +4008,7 @@
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B72" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C72" t="s">
         <v>189</v>
@@ -4021,7 +4026,7 @@
         <v>190</v>
       </c>
       <c r="H72" s="10" t="s">
-        <v>176</v>
+        <v>146</v>
       </c>
       <c r="I72" s="14" t="s">
         <v>193</v>
@@ -4029,7 +4034,7 @@
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B73" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C73" t="s">
         <v>189</v>
@@ -4047,7 +4052,7 @@
         <v>190</v>
       </c>
       <c r="H73" s="10" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="I73" s="14" t="s">
         <v>193</v>
@@ -4055,7 +4060,7 @@
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B74" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C74" t="s">
         <v>189</v>
@@ -4072,8 +4077,8 @@
       <c r="G74" s="13" t="s">
         <v>190</v>
       </c>
-      <c r="H74" s="10" t="s">
-        <v>148</v>
+      <c r="H74" s="16" t="s">
+        <v>154</v>
       </c>
       <c r="I74" s="14" t="s">
         <v>193</v>
@@ -4081,7 +4086,7 @@
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B75" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C75" t="s">
         <v>189</v>
@@ -4098,100 +4103,100 @@
       <c r="G75" s="13" t="s">
         <v>190</v>
       </c>
-      <c r="H75" s="16" t="s">
-        <v>154</v>
+      <c r="H75" s="11" t="s">
+        <v>150</v>
       </c>
       <c r="I75" s="14" t="s">
         <v>193</v>
       </c>
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A76" t="s">
+        <v>200</v>
+      </c>
       <c r="B76" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C76" t="s">
-        <v>189</v>
+        <v>202</v>
       </c>
       <c r="D76" s="5" t="s">
-        <v>16</v>
+        <v>203</v>
       </c>
       <c r="E76" s="5" t="s">
-        <v>16</v>
+        <v>203</v>
       </c>
       <c r="F76" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="G76" s="13" t="s">
-        <v>190</v>
-      </c>
-      <c r="H76" s="11" t="s">
-        <v>150</v>
+        <v>204</v>
+      </c>
+      <c r="G76" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="H76" s="10" t="s">
+        <v>205</v>
       </c>
       <c r="I76" s="14" t="s">
-        <v>193</v>
+        <v>206</v>
       </c>
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A77" t="s">
-        <v>200</v>
-      </c>
       <c r="B77" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="C77" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="D77" s="5" t="s">
-        <v>203</v>
+        <v>16</v>
       </c>
       <c r="E77" s="5" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="F77" s="5" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="G77" s="8" t="s">
         <v>11</v>
       </c>
       <c r="H77" s="10" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="I77" s="14" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B78" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="C78" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="D78" s="5" t="s">
         <v>16</v>
       </c>
       <c r="E78" s="5" t="s">
-        <v>209</v>
+        <v>16</v>
       </c>
       <c r="F78" s="5" t="s">
-        <v>210</v>
+        <v>16</v>
       </c>
       <c r="G78" s="8" t="s">
         <v>11</v>
       </c>
       <c r="H78" s="10" t="s">
-        <v>211</v>
-      </c>
-      <c r="I78" s="14" t="s">
-        <v>212</v>
+        <v>16</v>
+      </c>
+      <c r="I78" s="13" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B79" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="C79" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="D79" s="5" t="s">
         <v>16</v>
@@ -4214,10 +4219,10 @@
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B80" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C80" t="s">
-        <v>208</v>
+        <v>217</v>
       </c>
       <c r="D80" s="5" t="s">
         <v>16</v>
@@ -4240,10 +4245,10 @@
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B81" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C81" t="s">
-        <v>217</v>
+        <v>208</v>
       </c>
       <c r="D81" s="5" t="s">
         <v>16</v>
@@ -4266,62 +4271,62 @@
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B82" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C82" t="s">
-        <v>208</v>
+        <v>219</v>
       </c>
       <c r="D82" s="5" t="s">
-        <v>16</v>
+        <v>220</v>
       </c>
       <c r="E82" s="5" t="s">
-        <v>16</v>
+        <v>220</v>
       </c>
       <c r="F82" s="5" t="s">
-        <v>16</v>
+        <v>220</v>
       </c>
       <c r="G82" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="H82" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="I82" s="13" t="s">
-        <v>128</v>
+      <c r="H82" s="11" t="s">
+        <v>205</v>
+      </c>
+      <c r="I82" s="14" t="s">
+        <v>221</v>
       </c>
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B83" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="C83" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="D83" s="5" t="s">
-        <v>220</v>
+        <v>16</v>
       </c>
       <c r="E83" s="5" t="s">
-        <v>220</v>
+        <v>16</v>
       </c>
       <c r="F83" s="5" t="s">
-        <v>220</v>
-      </c>
-      <c r="G83" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="H83" s="11" t="s">
-        <v>205</v>
-      </c>
-      <c r="I83" s="14" t="s">
-        <v>221</v>
+        <v>204</v>
+      </c>
+      <c r="G83" s="13" t="s">
+        <v>223</v>
+      </c>
+      <c r="H83" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="I83" s="13" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B84" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="C84" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="D84" s="5" t="s">
         <v>16</v>
@@ -4330,33 +4335,33 @@
         <v>16</v>
       </c>
       <c r="F84" s="5" t="s">
-        <v>204</v>
-      </c>
-      <c r="G84" s="13" t="s">
-        <v>223</v>
+        <v>16</v>
+      </c>
+      <c r="G84" s="8" t="s">
+        <v>11</v>
       </c>
       <c r="H84" s="10" t="s">
         <v>16</v>
       </c>
       <c r="I84" s="13" t="s">
-        <v>31</v>
+        <v>225</v>
       </c>
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B85" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="C85" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D85" s="5" t="s">
         <v>16</v>
       </c>
       <c r="E85" s="5" t="s">
-        <v>16</v>
+        <v>226</v>
       </c>
       <c r="F85" s="5" t="s">
-        <v>16</v>
+        <v>226</v>
       </c>
       <c r="G85" s="8" t="s">
         <v>11</v>
@@ -4365,41 +4370,36 @@
         <v>16</v>
       </c>
       <c r="I85" s="13" t="s">
-        <v>225</v>
+        <v>31</v>
       </c>
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B86" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C86" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="D86" s="5" t="s">
         <v>16</v>
       </c>
       <c r="E86" s="5" t="s">
-        <v>226</v>
+        <v>16</v>
       </c>
       <c r="F86" s="5" t="s">
-        <v>226</v>
-      </c>
-      <c r="G86" s="8" t="s">
-        <v>11</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="G86" s="8"/>
       <c r="H86" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="I86" s="13" t="s">
-        <v>31</v>
+        <v>146</v>
+      </c>
+      <c r="I86" s="8" t="s">
+        <v>229</v>
       </c>
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B87" t="s">
-        <v>227</v>
-      </c>
-      <c r="C87" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="D87" s="5" t="s">
         <v>16</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="G87" s="8"/>
       <c r="H87" s="10" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="I87" s="8" t="s">
         <v>229</v>
@@ -4420,7 +4420,7 @@
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B88" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="D88" s="5" t="s">
         <v>16</v>
@@ -4432,8 +4432,8 @@
         <v>16</v>
       </c>
       <c r="G88" s="8"/>
-      <c r="H88" s="10" t="s">
-        <v>148</v>
+      <c r="H88" s="11" t="s">
+        <v>150</v>
       </c>
       <c r="I88" s="8" t="s">
         <v>229</v>
@@ -4441,7 +4441,7 @@
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B89" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="D89" s="5" t="s">
         <v>16</v>
@@ -4453,69 +4453,72 @@
         <v>16</v>
       </c>
       <c r="G89" s="8"/>
-      <c r="H89" s="11" t="s">
-        <v>150</v>
+      <c r="H89" s="10" t="s">
+        <v>154</v>
       </c>
       <c r="I89" s="8" t="s">
         <v>229</v>
       </c>
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A90" t="s">
+        <v>233</v>
+      </c>
       <c r="B90" t="s">
-        <v>232</v>
+        <v>234</v>
+      </c>
+      <c r="C90" t="s">
+        <v>235</v>
       </c>
       <c r="D90" s="5" t="s">
-        <v>16</v>
+        <v>236</v>
       </c>
       <c r="E90" s="5" t="s">
-        <v>16</v>
+        <v>236</v>
       </c>
       <c r="F90" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="G90" s="8"/>
+        <v>236</v>
+      </c>
+      <c r="G90" s="13" t="s">
+        <v>237</v>
+      </c>
       <c r="H90" s="10" t="s">
-        <v>154</v>
-      </c>
-      <c r="I90" s="8" t="s">
-        <v>229</v>
+        <v>238</v>
+      </c>
+      <c r="I90" s="13" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A91" t="s">
-        <v>233</v>
-      </c>
       <c r="B91" t="s">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="C91" t="s">
         <v>235</v>
       </c>
       <c r="D91" s="5" t="s">
-        <v>236</v>
+        <v>16</v>
       </c>
       <c r="E91" s="5" t="s">
-        <v>236</v>
+        <v>16</v>
       </c>
       <c r="F91" s="5" t="s">
-        <v>236</v>
+        <v>16</v>
       </c>
       <c r="G91" s="13" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="H91" s="10" t="s">
-        <v>238</v>
-      </c>
-      <c r="I91" s="13" t="s">
-        <v>128</v>
-      </c>
+        <v>244</v>
+      </c>
+      <c r="I91" s="13"/>
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B92" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="C92" t="s">
-        <v>235</v>
+        <v>246</v>
       </c>
       <c r="D92" s="5" t="s">
         <v>16</v>
@@ -4526,22 +4529,20 @@
       <c r="F92" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G92" s="13" t="s">
-        <v>240</v>
+      <c r="G92" s="8" t="s">
+        <v>11</v>
       </c>
       <c r="H92" s="10" t="s">
-        <v>238</v>
-      </c>
-      <c r="I92" s="13" t="s">
-        <v>128</v>
-      </c>
+        <v>247</v>
+      </c>
+      <c r="I92" s="13"/>
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B93" t="s">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="C93" t="s">
-        <v>235</v>
+        <v>246</v>
       </c>
       <c r="D93" s="5" t="s">
         <v>16</v>
@@ -4552,22 +4553,20 @@
       <c r="F93" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G93" s="13" t="s">
-        <v>240</v>
+      <c r="G93" s="8" t="s">
+        <v>11</v>
       </c>
       <c r="H93" s="10" t="s">
-        <v>238</v>
-      </c>
-      <c r="I93" s="13" t="s">
-        <v>128</v>
-      </c>
+        <v>249</v>
+      </c>
+      <c r="I93" s="13"/>
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B94" t="s">
-        <v>242</v>
+        <v>250</v>
       </c>
       <c r="C94" t="s">
-        <v>235</v>
+        <v>250</v>
       </c>
       <c r="D94" s="5" t="s">
         <v>16</v>
@@ -4578,22 +4577,20 @@
       <c r="F94" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G94" s="13" t="s">
-        <v>240</v>
+      <c r="G94" s="8" t="s">
+        <v>11</v>
       </c>
       <c r="H94" s="10" t="s">
-        <v>238</v>
-      </c>
-      <c r="I94" s="13" t="s">
-        <v>128</v>
-      </c>
+        <v>251</v>
+      </c>
+      <c r="I94" s="13"/>
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B95" t="s">
-        <v>243</v>
+        <v>252</v>
       </c>
       <c r="C95" t="s">
-        <v>235</v>
+        <v>252</v>
       </c>
       <c r="D95" s="5" t="s">
         <v>16</v>
@@ -4604,181 +4601,185 @@
       <c r="F95" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G95" s="13" t="s">
-        <v>240</v>
+      <c r="G95" s="8" t="s">
+        <v>11</v>
       </c>
       <c r="H95" s="10" t="s">
-        <v>244</v>
+        <v>253</v>
       </c>
       <c r="I95" s="13"/>
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B96" t="s">
-        <v>245</v>
+        <v>254</v>
       </c>
       <c r="C96" t="s">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="D96" s="5" t="s">
-        <v>16</v>
+        <v>255</v>
       </c>
       <c r="E96" s="5" t="s">
-        <v>16</v>
+        <v>255</v>
       </c>
       <c r="F96" s="5" t="s">
-        <v>16</v>
+        <v>255</v>
       </c>
       <c r="G96" s="8" t="s">
         <v>11</v>
       </c>
       <c r="H96" s="10" t="s">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="I96" s="13"/>
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A97" t="s">
+        <v>257</v>
+      </c>
       <c r="B97" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
       <c r="C97" t="s">
-        <v>246</v>
+        <v>258</v>
       </c>
       <c r="D97" s="5" t="s">
-        <v>16</v>
+        <v>258</v>
       </c>
       <c r="E97" s="5" t="s">
-        <v>16</v>
+        <v>258</v>
       </c>
       <c r="F97" s="5" t="s">
-        <v>16</v>
+        <v>258</v>
       </c>
       <c r="G97" s="8" t="s">
         <v>11</v>
       </c>
       <c r="H97" s="10" t="s">
-        <v>249</v>
-      </c>
-      <c r="I97" s="13"/>
+        <v>16</v>
+      </c>
+      <c r="I97" s="13" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B98" t="s">
-        <v>250</v>
+        <v>259</v>
       </c>
       <c r="C98" t="s">
-        <v>250</v>
+        <v>259</v>
       </c>
       <c r="D98" s="5" t="s">
-        <v>16</v>
+        <v>260</v>
       </c>
       <c r="E98" s="5" t="s">
-        <v>16</v>
+        <v>260</v>
       </c>
       <c r="F98" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="G98" s="8" t="s">
-        <v>11</v>
+        <v>260</v>
+      </c>
+      <c r="G98" s="13" t="s">
+        <v>237</v>
       </c>
       <c r="H98" s="10" t="s">
-        <v>251</v>
-      </c>
-      <c r="I98" s="13"/>
+        <v>16</v>
+      </c>
+      <c r="I98" s="13" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B99" t="s">
-        <v>252</v>
+        <v>261</v>
       </c>
       <c r="C99" t="s">
-        <v>252</v>
+        <v>261</v>
       </c>
       <c r="D99" s="5" t="s">
-        <v>16</v>
+        <v>260</v>
       </c>
       <c r="E99" s="5" t="s">
-        <v>16</v>
+        <v>260</v>
       </c>
       <c r="F99" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="G99" s="8" t="s">
-        <v>11</v>
+        <v>260</v>
+      </c>
+      <c r="G99" s="13" t="s">
+        <v>237</v>
       </c>
       <c r="H99" s="10" t="s">
-        <v>253</v>
-      </c>
-      <c r="I99" s="13"/>
+        <v>16</v>
+      </c>
+      <c r="I99" s="13" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B100" t="s">
-        <v>254</v>
+        <v>262</v>
       </c>
       <c r="C100" t="s">
-        <v>254</v>
+        <v>262</v>
       </c>
       <c r="D100" s="5" t="s">
-        <v>255</v>
+        <v>16</v>
       </c>
       <c r="E100" s="5" t="s">
-        <v>255</v>
+        <v>16</v>
       </c>
       <c r="F100" s="5" t="s">
-        <v>255</v>
+        <v>16</v>
       </c>
       <c r="G100" s="8" t="s">
         <v>11</v>
       </c>
       <c r="H100" s="10" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="I100" s="13"/>
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A101" t="s">
-        <v>257</v>
-      </c>
       <c r="B101" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="C101" t="s">
-        <v>258</v>
+        <v>265</v>
       </c>
       <c r="D101" s="5" t="s">
-        <v>258</v>
+        <v>16</v>
       </c>
       <c r="E101" s="5" t="s">
-        <v>258</v>
+        <v>16</v>
       </c>
       <c r="F101" s="5" t="s">
-        <v>258</v>
+        <v>16</v>
       </c>
       <c r="G101" s="8" t="s">
         <v>11</v>
       </c>
       <c r="H101" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="I101" s="13" t="s">
-        <v>31</v>
-      </c>
+        <v>266</v>
+      </c>
+      <c r="I101" s="13"/>
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B102" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="C102" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="D102" s="5" t="s">
-        <v>260</v>
+        <v>16</v>
       </c>
       <c r="E102" s="5" t="s">
-        <v>260</v>
+        <v>16</v>
       </c>
       <c r="F102" s="5" t="s">
-        <v>260</v>
+        <v>16</v>
       </c>
       <c r="G102" s="13" t="s">
-        <v>237</v>
+        <v>268</v>
       </c>
       <c r="H102" s="10" t="s">
         <v>16</v>
@@ -4789,22 +4790,22 @@
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B103" t="s">
-        <v>261</v>
+        <v>269</v>
       </c>
       <c r="C103" t="s">
-        <v>261</v>
+        <v>269</v>
       </c>
       <c r="D103" s="5" t="s">
-        <v>260</v>
+        <v>16</v>
       </c>
       <c r="E103" s="5" t="s">
-        <v>260</v>
+        <v>16</v>
       </c>
       <c r="F103" s="5" t="s">
-        <v>260</v>
+        <v>16</v>
       </c>
       <c r="G103" s="13" t="s">
-        <v>237</v>
+        <v>268</v>
       </c>
       <c r="H103" s="10" t="s">
         <v>16</v>
@@ -4815,10 +4816,10 @@
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B104" t="s">
-        <v>262</v>
+        <v>270</v>
       </c>
       <c r="C104" t="s">
-        <v>262</v>
+        <v>270</v>
       </c>
       <c r="D104" s="5" t="s">
         <v>16</v>
@@ -4829,20 +4830,22 @@
       <c r="F104" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G104" s="8" t="s">
-        <v>11</v>
+      <c r="G104" s="13" t="s">
+        <v>271</v>
       </c>
       <c r="H104" s="10" t="s">
-        <v>263</v>
-      </c>
-      <c r="I104" s="13"/>
+        <v>16</v>
+      </c>
+      <c r="I104" s="13" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B105" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
       <c r="C105" t="s">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="D105" s="5" t="s">
         <v>16</v>
@@ -4853,58 +4856,58 @@
       <c r="F105" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G105" s="8" t="s">
-        <v>11</v>
+      <c r="G105" s="13" t="s">
+        <v>271</v>
       </c>
       <c r="H105" s="10" t="s">
-        <v>266</v>
-      </c>
-      <c r="I105" s="13"/>
+        <v>16</v>
+      </c>
+      <c r="I105" s="13" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="106" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B106" t="s">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="C106" t="s">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="D106" s="5" t="s">
         <v>16</v>
       </c>
       <c r="E106" s="5" t="s">
-        <v>16</v>
+        <v>274</v>
       </c>
       <c r="F106" s="5" t="s">
-        <v>16</v>
+        <v>275</v>
       </c>
       <c r="G106" s="13" t="s">
-        <v>268</v>
+        <v>128</v>
       </c>
       <c r="H106" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="I106" s="13" t="s">
-        <v>31</v>
-      </c>
+        <v>276</v>
+      </c>
+      <c r="I106" s="13"/>
     </row>
     <row r="107" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B107" t="s">
-        <v>269</v>
+        <v>277</v>
       </c>
       <c r="C107" t="s">
-        <v>269</v>
+        <v>277</v>
       </c>
       <c r="D107" s="5" t="s">
         <v>16</v>
       </c>
       <c r="E107" s="5" t="s">
-        <v>16</v>
+        <v>278</v>
       </c>
       <c r="F107" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="G107" s="13" t="s">
-        <v>268</v>
+        <v>278</v>
+      </c>
+      <c r="G107" s="8" t="s">
+        <v>11</v>
       </c>
       <c r="H107" s="10" t="s">
         <v>16</v>
@@ -4915,22 +4918,22 @@
     </row>
     <row r="108" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B108" t="s">
-        <v>270</v>
+        <v>279</v>
       </c>
       <c r="C108" t="s">
-        <v>270</v>
+        <v>279</v>
       </c>
       <c r="D108" s="5" t="s">
         <v>16</v>
       </c>
       <c r="E108" s="5" t="s">
-        <v>16</v>
+        <v>278</v>
       </c>
       <c r="F108" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="G108" s="13" t="s">
-        <v>271</v>
+        <v>279</v>
+      </c>
+      <c r="G108" s="8" t="s">
+        <v>11</v>
       </c>
       <c r="H108" s="10" t="s">
         <v>16</v>
@@ -4941,10 +4944,10 @@
     </row>
     <row r="109" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B109" t="s">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="C109" t="s">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="D109" s="5" t="s">
         <v>16</v>
@@ -4956,7 +4959,7 @@
         <v>16</v>
       </c>
       <c r="G109" s="13" t="s">
-        <v>271</v>
+        <v>281</v>
       </c>
       <c r="H109" s="10" t="s">
         <v>16</v>
@@ -4966,47 +4969,52 @@
       </c>
     </row>
     <row r="110" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A110" t="s">
+        <v>282</v>
+      </c>
       <c r="B110" t="s">
-        <v>273</v>
+        <v>283</v>
       </c>
       <c r="C110" t="s">
-        <v>273</v>
+        <v>283</v>
       </c>
       <c r="D110" s="5" t="s">
-        <v>16</v>
+        <v>284</v>
       </c>
       <c r="E110" s="5" t="s">
-        <v>274</v>
+        <v>285</v>
       </c>
       <c r="F110" s="5" t="s">
-        <v>275</v>
-      </c>
-      <c r="G110" s="13" t="s">
-        <v>128</v>
+        <v>285</v>
+      </c>
+      <c r="G110" s="8" t="s">
+        <v>11</v>
       </c>
       <c r="H110" s="10" t="s">
-        <v>276</v>
-      </c>
-      <c r="I110" s="13"/>
+        <v>16</v>
+      </c>
+      <c r="I110" s="13" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B111" t="s">
-        <v>277</v>
+        <v>286</v>
       </c>
       <c r="C111" t="s">
-        <v>277</v>
+        <v>286</v>
       </c>
       <c r="D111" s="5" t="s">
-        <v>16</v>
+        <v>284</v>
       </c>
       <c r="E111" s="5" t="s">
-        <v>278</v>
+        <v>287</v>
       </c>
       <c r="F111" s="5" t="s">
-        <v>278</v>
-      </c>
-      <c r="G111" s="8" t="s">
-        <v>11</v>
+        <v>287</v>
+      </c>
+      <c r="G111" s="13" t="s">
+        <v>128</v>
       </c>
       <c r="H111" s="10" t="s">
         <v>16</v>
@@ -5017,48 +5025,49 @@
     </row>
     <row r="112" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B112" t="s">
-        <v>279</v>
+        <v>288</v>
       </c>
       <c r="C112" t="s">
-        <v>279</v>
+        <v>289</v>
       </c>
       <c r="D112" s="5" t="s">
         <v>16</v>
       </c>
       <c r="E112" s="5" t="s">
-        <v>278</v>
+        <v>287</v>
       </c>
       <c r="F112" s="5" t="s">
-        <v>279</v>
-      </c>
-      <c r="G112" s="8" t="s">
-        <v>11</v>
+        <v>287</v>
+      </c>
+      <c r="G112" s="13" t="s">
+        <v>128</v>
       </c>
       <c r="H112" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="I112" s="13" t="s">
-        <v>31</v>
-      </c>
+        <v>290</v>
+      </c>
+      <c r="I112" s="13"/>
     </row>
     <row r="113" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A113" t="s">
+        <v>291</v>
+      </c>
       <c r="B113" t="s">
-        <v>280</v>
+        <v>292</v>
       </c>
       <c r="C113" t="s">
-        <v>280</v>
+        <v>292</v>
       </c>
       <c r="D113" s="5" t="s">
         <v>16</v>
       </c>
       <c r="E113" s="5" t="s">
-        <v>16</v>
+        <v>293</v>
       </c>
       <c r="F113" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="G113" s="13" t="s">
-        <v>281</v>
+        <v>293</v>
+      </c>
+      <c r="G113" s="8" t="s">
+        <v>11</v>
       </c>
       <c r="H113" s="10" t="s">
         <v>16</v>
@@ -5068,52 +5077,47 @@
       </c>
     </row>
     <row r="114" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A114" t="s">
-        <v>282</v>
-      </c>
       <c r="B114" t="s">
-        <v>283</v>
+        <v>294</v>
       </c>
       <c r="C114" t="s">
-        <v>283</v>
+        <v>295</v>
       </c>
       <c r="D114" s="5" t="s">
-        <v>284</v>
+        <v>16</v>
       </c>
       <c r="E114" s="5" t="s">
-        <v>285</v>
+        <v>296</v>
       </c>
       <c r="F114" s="5" t="s">
-        <v>285</v>
+        <v>296</v>
       </c>
       <c r="G114" s="8" t="s">
         <v>11</v>
       </c>
       <c r="H114" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="I114" s="13" t="s">
-        <v>31</v>
-      </c>
+        <v>297</v>
+      </c>
+      <c r="I114" s="13"/>
     </row>
     <row r="115" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B115" t="s">
-        <v>286</v>
+        <v>298</v>
       </c>
       <c r="C115" t="s">
-        <v>286</v>
+        <v>298</v>
       </c>
       <c r="D115" s="5" t="s">
-        <v>284</v>
+        <v>16</v>
       </c>
       <c r="E115" s="5" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="F115" s="5" t="s">
-        <v>287</v>
-      </c>
-      <c r="G115" s="13" t="s">
-        <v>128</v>
+        <v>293</v>
+      </c>
+      <c r="G115" s="8" t="s">
+        <v>11</v>
       </c>
       <c r="H115" s="10" t="s">
         <v>16</v>
@@ -5124,46 +5128,45 @@
     </row>
     <row r="116" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B116" t="s">
-        <v>288</v>
+        <v>299</v>
       </c>
       <c r="C116" t="s">
-        <v>289</v>
+        <v>299</v>
       </c>
       <c r="D116" s="5" t="s">
         <v>16</v>
       </c>
       <c r="E116" s="5" t="s">
-        <v>287</v>
+        <v>300</v>
       </c>
       <c r="F116" s="5" t="s">
-        <v>287</v>
-      </c>
-      <c r="G116" s="13" t="s">
-        <v>128</v>
+        <v>300</v>
+      </c>
+      <c r="G116" s="8" t="s">
+        <v>11</v>
       </c>
       <c r="H116" s="10" t="s">
-        <v>290</v>
-      </c>
-      <c r="I116" s="13"/>
+        <v>16</v>
+      </c>
+      <c r="I116" s="13" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="117" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A117" t="s">
-        <v>291</v>
-      </c>
       <c r="B117" t="s">
-        <v>292</v>
+        <v>301</v>
       </c>
       <c r="C117" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="D117" s="5" t="s">
         <v>16</v>
       </c>
       <c r="E117" s="5" t="s">
-        <v>293</v>
+        <v>16</v>
       </c>
       <c r="F117" s="5" t="s">
-        <v>293</v>
+        <v>16</v>
       </c>
       <c r="G117" s="8" t="s">
         <v>11</v>
@@ -5171,13 +5174,11 @@
       <c r="H117" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="I117" s="13" t="s">
-        <v>31</v>
-      </c>
+      <c r="I117" s="8"/>
     </row>
     <row r="118" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B118" t="s">
-        <v>294</v>
+        <v>302</v>
       </c>
       <c r="C118" t="s">
         <v>295</v>
@@ -5186,34 +5187,36 @@
         <v>16</v>
       </c>
       <c r="E118" s="5" t="s">
-        <v>296</v>
+        <v>16</v>
       </c>
       <c r="F118" s="5" t="s">
-        <v>296</v>
+        <v>16</v>
       </c>
       <c r="G118" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="H118" s="10" t="s">
-        <v>297</v>
-      </c>
-      <c r="I118" s="13"/>
+      <c r="H118" s="11" t="s">
+        <v>303</v>
+      </c>
+      <c r="I118" s="8" t="s">
+        <v>303</v>
+      </c>
     </row>
     <row r="119" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B119" t="s">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="C119" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="D119" s="5" t="s">
         <v>16</v>
       </c>
       <c r="E119" s="5" t="s">
-        <v>293</v>
+        <v>16</v>
       </c>
       <c r="F119" s="5" t="s">
-        <v>293</v>
+        <v>16</v>
       </c>
       <c r="G119" s="8" t="s">
         <v>11</v>
@@ -5221,152 +5224,160 @@
       <c r="H119" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="I119" s="13" t="s">
-        <v>31</v>
-      </c>
+      <c r="I119" s="8"/>
     </row>
     <row r="120" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B120" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="C120" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="D120" s="5" t="s">
         <v>16</v>
       </c>
       <c r="E120" s="5" t="s">
-        <v>300</v>
+        <v>16</v>
       </c>
       <c r="F120" s="5" t="s">
-        <v>300</v>
+        <v>16</v>
       </c>
       <c r="G120" s="8" t="s">
         <v>11</v>
       </c>
       <c r="H120" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="I120" s="13" t="s">
-        <v>31</v>
-      </c>
+        <v>306</v>
+      </c>
+      <c r="I120" s="8"/>
     </row>
     <row r="121" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B121" t="s">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="C121" t="s">
-        <v>295</v>
+        <v>308</v>
       </c>
       <c r="D121" s="5" t="s">
-        <v>16</v>
+        <v>309</v>
       </c>
       <c r="E121" s="5" t="s">
-        <v>16</v>
+        <v>310</v>
       </c>
       <c r="F121" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="G121" s="8" t="s">
-        <v>11</v>
+        <v>310</v>
+      </c>
+      <c r="G121" s="13" t="s">
+        <v>71</v>
       </c>
       <c r="H121" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="I121" s="8"/>
+      <c r="I121" s="13" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="122" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A122" t="s">
+        <v>311</v>
+      </c>
       <c r="B122" t="s">
-        <v>302</v>
+        <v>312</v>
       </c>
       <c r="C122" t="s">
-        <v>295</v>
+        <v>312</v>
       </c>
       <c r="D122" s="5" t="s">
         <v>16</v>
       </c>
       <c r="E122" s="5" t="s">
-        <v>16</v>
+        <v>313</v>
       </c>
       <c r="F122" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="G122" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="H122" s="11" t="s">
-        <v>303</v>
-      </c>
-      <c r="I122" s="8" t="s">
-        <v>303</v>
+        <v>313</v>
+      </c>
+      <c r="G122" s="13" t="s">
+        <v>314</v>
+      </c>
+      <c r="H122" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="I122" s="13" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="123" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B123" t="s">
-        <v>304</v>
+        <v>315</v>
       </c>
       <c r="C123" t="s">
-        <v>295</v>
+        <v>316</v>
       </c>
       <c r="D123" s="5" t="s">
         <v>16</v>
       </c>
       <c r="E123" s="5" t="s">
-        <v>16</v>
+        <v>79</v>
       </c>
       <c r="F123" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="G123" s="8" t="s">
-        <v>11</v>
+        <v>79</v>
+      </c>
+      <c r="G123" s="13" t="s">
+        <v>237</v>
       </c>
       <c r="H123" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="I123" s="8"/>
+      <c r="I123" s="13" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="124" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B124" t="s">
-        <v>305</v>
+        <v>317</v>
       </c>
       <c r="C124" t="s">
-        <v>305</v>
+        <v>317</v>
       </c>
       <c r="D124" s="5" t="s">
         <v>16</v>
       </c>
       <c r="E124" s="5" t="s">
-        <v>16</v>
+        <v>79</v>
       </c>
       <c r="F124" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="G124" s="8" t="s">
-        <v>11</v>
+        <v>79</v>
+      </c>
+      <c r="G124" s="13" t="s">
+        <v>237</v>
       </c>
       <c r="H124" s="10" t="s">
-        <v>306</v>
-      </c>
-      <c r="I124" s="8"/>
+        <v>16</v>
+      </c>
+      <c r="I124" s="13" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="125" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A125" t="s">
+        <v>318</v>
+      </c>
       <c r="B125" t="s">
-        <v>307</v>
+        <v>319</v>
       </c>
       <c r="C125" t="s">
-        <v>308</v>
+        <v>320</v>
       </c>
       <c r="D125" s="5" t="s">
-        <v>309</v>
+        <v>16</v>
       </c>
       <c r="E125" s="5" t="s">
-        <v>310</v>
+        <v>16</v>
       </c>
       <c r="F125" s="5" t="s">
-        <v>310</v>
+        <v>16</v>
       </c>
       <c r="G125" s="13" t="s">
-        <v>71</v>
+        <v>128</v>
       </c>
       <c r="H125" s="10" t="s">
         <v>16</v>
@@ -5376,26 +5387,23 @@
       </c>
     </row>
     <row r="126" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A126" t="s">
-        <v>311</v>
-      </c>
       <c r="B126" t="s">
-        <v>312</v>
+        <v>321</v>
       </c>
       <c r="C126" t="s">
-        <v>312</v>
+        <v>321</v>
       </c>
       <c r="D126" s="5" t="s">
-        <v>16</v>
+        <v>322</v>
       </c>
       <c r="E126" s="5" t="s">
-        <v>313</v>
+        <v>16</v>
       </c>
       <c r="F126" s="5" t="s">
-        <v>313</v>
-      </c>
-      <c r="G126" s="13" t="s">
-        <v>314</v>
+        <v>16</v>
+      </c>
+      <c r="G126" s="8" t="s">
+        <v>11</v>
       </c>
       <c r="H126" s="10" t="s">
         <v>16</v>
@@ -5406,22 +5414,22 @@
     </row>
     <row r="127" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B127" t="s">
-        <v>315</v>
+        <v>323</v>
       </c>
       <c r="C127" t="s">
-        <v>316</v>
+        <v>323</v>
       </c>
       <c r="D127" s="5" t="s">
-        <v>16</v>
+        <v>324</v>
       </c>
       <c r="E127" s="5" t="s">
-        <v>79</v>
+        <v>16</v>
       </c>
       <c r="F127" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="G127" s="13" t="s">
-        <v>237</v>
+        <v>16</v>
+      </c>
+      <c r="G127" s="8" t="s">
+        <v>11</v>
       </c>
       <c r="H127" s="10" t="s">
         <v>16</v>
@@ -5432,22 +5440,22 @@
     </row>
     <row r="128" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B128" t="s">
-        <v>317</v>
+        <v>325</v>
       </c>
       <c r="C128" t="s">
-        <v>317</v>
+        <v>325</v>
       </c>
       <c r="D128" s="5" t="s">
-        <v>16</v>
+        <v>326</v>
       </c>
       <c r="E128" s="5" t="s">
-        <v>79</v>
+        <v>327</v>
       </c>
       <c r="F128" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="G128" s="13" t="s">
-        <v>237</v>
+        <v>327</v>
+      </c>
+      <c r="G128" s="8" t="s">
+        <v>11</v>
       </c>
       <c r="H128" s="10" t="s">
         <v>16</v>
@@ -5457,17 +5465,14 @@
       </c>
     </row>
     <row r="129" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A129" t="s">
-        <v>318</v>
-      </c>
       <c r="B129" t="s">
-        <v>319</v>
+        <v>328</v>
       </c>
       <c r="C129" t="s">
-        <v>320</v>
+        <v>328</v>
       </c>
       <c r="D129" s="5" t="s">
-        <v>16</v>
+        <v>329</v>
       </c>
       <c r="E129" s="5" t="s">
         <v>16</v>
@@ -5475,8 +5480,8 @@
       <c r="F129" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G129" s="13" t="s">
-        <v>128</v>
+      <c r="G129" s="8" t="s">
+        <v>11</v>
       </c>
       <c r="H129" s="10" t="s">
         <v>16</v>
@@ -5486,14 +5491,17 @@
       </c>
     </row>
     <row r="130" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A130" t="s">
+        <v>330</v>
+      </c>
       <c r="B130" t="s">
-        <v>321</v>
+        <v>331</v>
       </c>
       <c r="C130" t="s">
-        <v>321</v>
+        <v>331</v>
       </c>
       <c r="D130" s="5" t="s">
-        <v>322</v>
+        <v>16</v>
       </c>
       <c r="E130" s="5" t="s">
         <v>16</v>
@@ -5501,77 +5509,73 @@
       <c r="F130" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G130" s="8" t="s">
-        <v>11</v>
+      <c r="G130" s="13" t="s">
+        <v>332</v>
       </c>
       <c r="H130" s="10" t="s">
-        <v>16</v>
+        <v>333</v>
       </c>
       <c r="I130" s="13" t="s">
-        <v>31</v>
+        <v>334</v>
       </c>
     </row>
     <row r="131" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B131" t="s">
-        <v>323</v>
+        <v>335</v>
       </c>
       <c r="C131" t="s">
-        <v>323</v>
+        <v>335</v>
       </c>
       <c r="D131" s="5" t="s">
-        <v>324</v>
+        <v>336</v>
       </c>
       <c r="E131" s="5" t="s">
-        <v>16</v>
+        <v>337</v>
       </c>
       <c r="F131" s="5" t="s">
-        <v>16</v>
+        <v>337</v>
       </c>
       <c r="G131" s="8" t="s">
         <v>11</v>
       </c>
       <c r="H131" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="I131" s="13" t="s">
-        <v>31</v>
-      </c>
+        <v>333</v>
+      </c>
+      <c r="I131" s="13"/>
     </row>
     <row r="132" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B132" t="s">
-        <v>325</v>
+        <v>338</v>
       </c>
       <c r="C132" t="s">
-        <v>325</v>
+        <v>339</v>
       </c>
       <c r="D132" s="5" t="s">
-        <v>326</v>
+        <v>16</v>
       </c>
       <c r="E132" s="5" t="s">
-        <v>327</v>
+        <v>340</v>
       </c>
       <c r="F132" s="5" t="s">
-        <v>327</v>
+        <v>340</v>
       </c>
       <c r="G132" s="8" t="s">
         <v>11</v>
       </c>
       <c r="H132" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="I132" s="13" t="s">
-        <v>31</v>
-      </c>
+        <v>341</v>
+      </c>
+      <c r="I132" s="13"/>
     </row>
     <row r="133" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B133" t="s">
-        <v>328</v>
+        <v>342</v>
       </c>
       <c r="C133" t="s">
-        <v>328</v>
+        <v>343</v>
       </c>
       <c r="D133" s="5" t="s">
-        <v>329</v>
+        <v>16</v>
       </c>
       <c r="E133" s="5" t="s">
         <v>16</v>
@@ -5579,25 +5583,22 @@
       <c r="F133" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G133" s="8" t="s">
-        <v>11</v>
+      <c r="G133" s="13" t="s">
+        <v>332</v>
       </c>
       <c r="H133" s="10" t="s">
-        <v>16</v>
+        <v>344</v>
       </c>
       <c r="I133" s="13" t="s">
-        <v>31</v>
+        <v>345</v>
       </c>
     </row>
     <row r="134" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A134" t="s">
-        <v>330</v>
-      </c>
       <c r="B134" t="s">
-        <v>331</v>
+        <v>346</v>
       </c>
       <c r="C134" t="s">
-        <v>331</v>
+        <v>346</v>
       </c>
       <c r="D134" s="5" t="s">
         <v>16</v>
@@ -5608,70 +5609,73 @@
       <c r="F134" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G134" s="13" t="s">
-        <v>332</v>
+      <c r="G134" s="8" t="s">
+        <v>11</v>
       </c>
       <c r="H134" s="10" t="s">
-        <v>333</v>
-      </c>
-      <c r="I134" s="13" t="s">
-        <v>334</v>
-      </c>
+        <v>344</v>
+      </c>
+      <c r="I134" s="13"/>
     </row>
     <row r="135" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B135" t="s">
-        <v>335</v>
+        <v>347</v>
       </c>
       <c r="C135" t="s">
-        <v>335</v>
+        <v>348</v>
       </c>
       <c r="D135" s="5" t="s">
-        <v>336</v>
+        <v>16</v>
       </c>
       <c r="E135" s="5" t="s">
-        <v>337</v>
+        <v>349</v>
       </c>
       <c r="F135" s="5" t="s">
-        <v>337</v>
+        <v>350</v>
       </c>
       <c r="G135" s="8" t="s">
         <v>11</v>
       </c>
       <c r="H135" s="10" t="s">
-        <v>333</v>
+        <v>351</v>
       </c>
       <c r="I135" s="13"/>
     </row>
     <row r="136" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A136" t="s">
+        <v>352</v>
+      </c>
       <c r="B136" t="s">
-        <v>338</v>
+        <v>353</v>
       </c>
       <c r="C136" t="s">
-        <v>339</v>
+        <v>354</v>
       </c>
       <c r="D136" s="5" t="s">
-        <v>16</v>
+        <v>355</v>
       </c>
       <c r="E136" s="5" t="s">
-        <v>340</v>
+        <v>16</v>
       </c>
       <c r="F136" s="5" t="s">
-        <v>340</v>
-      </c>
-      <c r="G136" s="8" t="s">
-        <v>11</v>
+        <v>16</v>
+      </c>
+      <c r="G136" s="13" t="s">
+        <v>356</v>
       </c>
       <c r="H136" s="10" t="s">
-        <v>341</v>
-      </c>
-      <c r="I136" s="13"/>
+        <v>16</v>
+      </c>
+      <c r="I136" s="13" t="s">
+        <v>357</v>
+      </c>
     </row>
     <row r="137" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B137" t="s">
-        <v>342</v>
+        <v>358</v>
       </c>
       <c r="C137" t="s">
-        <v>343</v>
+        <v>358</v>
       </c>
       <c r="D137" s="5" t="s">
         <v>16</v>
@@ -5686,72 +5690,69 @@
         <v>332</v>
       </c>
       <c r="H137" s="10" t="s">
-        <v>344</v>
+        <v>16</v>
       </c>
       <c r="I137" s="13" t="s">
-        <v>345</v>
+        <v>357</v>
       </c>
     </row>
     <row r="138" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B138" t="s">
-        <v>346</v>
+        <v>359</v>
       </c>
       <c r="C138" t="s">
-        <v>346</v>
+        <v>359</v>
       </c>
       <c r="D138" s="5" t="s">
         <v>16</v>
       </c>
       <c r="E138" s="5" t="s">
-        <v>16</v>
+        <v>360</v>
       </c>
       <c r="F138" s="5" t="s">
-        <v>16</v>
+        <v>360</v>
       </c>
       <c r="G138" s="8" t="s">
         <v>11</v>
       </c>
       <c r="H138" s="10" t="s">
-        <v>344</v>
+        <v>361</v>
       </c>
       <c r="I138" s="13"/>
     </row>
     <row r="139" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B139" t="s">
-        <v>347</v>
+        <v>362</v>
       </c>
       <c r="C139" t="s">
-        <v>348</v>
+        <v>362</v>
       </c>
       <c r="D139" s="5" t="s">
         <v>16</v>
       </c>
       <c r="E139" s="5" t="s">
-        <v>349</v>
+        <v>363</v>
       </c>
       <c r="F139" s="5" t="s">
-        <v>350</v>
+        <v>363</v>
       </c>
       <c r="G139" s="8" t="s">
         <v>11</v>
       </c>
       <c r="H139" s="10" t="s">
-        <v>351</v>
+        <v>364</v>
       </c>
       <c r="I139" s="13"/>
     </row>
     <row r="140" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A140" t="s">
-        <v>352</v>
-      </c>
       <c r="B140" t="s">
-        <v>353</v>
+        <v>365</v>
       </c>
       <c r="C140" t="s">
-        <v>354</v>
+        <v>365</v>
       </c>
       <c r="D140" s="5" t="s">
-        <v>355</v>
+        <v>16</v>
       </c>
       <c r="E140" s="5" t="s">
         <v>16</v>
@@ -5760,21 +5761,19 @@
         <v>16</v>
       </c>
       <c r="G140" s="13" t="s">
-        <v>356</v>
+        <v>366</v>
       </c>
       <c r="H140" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="I140" s="13" t="s">
-        <v>357</v>
-      </c>
+      <c r="I140" s="13"/>
     </row>
     <row r="141" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B141" t="s">
-        <v>358</v>
+        <v>367</v>
       </c>
       <c r="C141" t="s">
-        <v>358</v>
+        <v>367</v>
       </c>
       <c r="D141" s="5" t="s">
         <v>16</v>
@@ -5785,70 +5784,76 @@
       <c r="F141" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G141" s="13" t="s">
-        <v>332</v>
+      <c r="G141" s="8" t="s">
+        <v>11</v>
       </c>
       <c r="H141" s="10" t="s">
         <v>16</v>
       </c>
       <c r="I141" s="13" t="s">
-        <v>357</v>
+        <v>119</v>
       </c>
     </row>
     <row r="142" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A142" t="s">
+        <v>368</v>
+      </c>
       <c r="B142" t="s">
-        <v>359</v>
+        <v>368</v>
       </c>
       <c r="C142" t="s">
-        <v>359</v>
+        <v>368</v>
       </c>
       <c r="D142" s="5" t="s">
-        <v>16</v>
+        <v>369</v>
       </c>
       <c r="E142" s="5" t="s">
-        <v>360</v>
+        <v>370</v>
       </c>
       <c r="F142" s="5" t="s">
-        <v>360</v>
+        <v>370</v>
       </c>
       <c r="G142" s="8" t="s">
         <v>11</v>
       </c>
       <c r="H142" s="10" t="s">
-        <v>361</v>
+        <v>16</v>
       </c>
       <c r="I142" s="13"/>
     </row>
     <row r="143" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A143" t="s">
+        <v>371</v>
+      </c>
       <c r="B143" t="s">
-        <v>362</v>
+        <v>372</v>
       </c>
       <c r="C143" t="s">
-        <v>362</v>
+        <v>373</v>
       </c>
       <c r="D143" s="5" t="s">
         <v>16</v>
       </c>
       <c r="E143" s="5" t="s">
-        <v>363</v>
+        <v>16</v>
       </c>
       <c r="F143" s="5" t="s">
-        <v>363</v>
-      </c>
-      <c r="G143" s="8" t="s">
-        <v>11</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="G143" s="8"/>
       <c r="H143" s="10" t="s">
-        <v>364</v>
-      </c>
-      <c r="I143" s="13"/>
+        <v>16</v>
+      </c>
+      <c r="I143" s="13" t="s">
+        <v>374</v>
+      </c>
     </row>
     <row r="144" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B144" t="s">
-        <v>365</v>
+        <v>375</v>
       </c>
       <c r="C144" t="s">
-        <v>365</v>
+        <v>376</v>
       </c>
       <c r="D144" s="5" t="s">
         <v>16</v>
@@ -5859,20 +5864,22 @@
       <c r="F144" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G144" s="13" t="s">
-        <v>366</v>
+      <c r="G144" s="8" t="s">
+        <v>11</v>
       </c>
       <c r="H144" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="I144" s="13"/>
+      <c r="I144" s="13" t="s">
+        <v>374</v>
+      </c>
     </row>
     <row r="145" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B145" t="s">
-        <v>367</v>
+        <v>377</v>
       </c>
       <c r="C145" t="s">
-        <v>367</v>
+        <v>75</v>
       </c>
       <c r="D145" s="5" t="s">
         <v>16</v>
@@ -5889,46 +5896,41 @@
       <c r="H145" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="I145" s="13" t="s">
-        <v>119</v>
-      </c>
+      <c r="I145" s="13"/>
     </row>
     <row r="146" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A146" t="s">
-        <v>368</v>
+        <v>378</v>
       </c>
       <c r="B146" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="C146" t="s">
-        <v>368</v>
+        <v>380</v>
       </c>
       <c r="D146" s="5" t="s">
-        <v>369</v>
+        <v>16</v>
       </c>
       <c r="E146" s="5" t="s">
-        <v>370</v>
+        <v>16</v>
       </c>
       <c r="F146" s="5" t="s">
-        <v>370</v>
+        <v>16</v>
       </c>
       <c r="G146" s="8" t="s">
         <v>11</v>
       </c>
       <c r="H146" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="I146" s="13"/>
+        <v>381</v>
+      </c>
+      <c r="I146" s="8"/>
     </row>
     <row r="147" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A147" t="s">
-        <v>371</v>
-      </c>
       <c r="B147" t="s">
-        <v>372</v>
+        <v>382</v>
       </c>
       <c r="C147" t="s">
-        <v>373</v>
+        <v>383</v>
       </c>
       <c r="D147" s="5" t="s">
         <v>16</v>
@@ -5939,20 +5941,20 @@
       <c r="F147" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G147" s="8"/>
+      <c r="G147" s="8" t="s">
+        <v>11</v>
+      </c>
       <c r="H147" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="I147" s="13" t="s">
-        <v>374</v>
-      </c>
+        <v>384</v>
+      </c>
+      <c r="I147" s="8"/>
     </row>
     <row r="148" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B148" t="s">
-        <v>375</v>
+        <v>385</v>
       </c>
       <c r="C148" t="s">
-        <v>376</v>
+        <v>385</v>
       </c>
       <c r="D148" s="5" t="s">
         <v>16</v>
@@ -5967,18 +5969,16 @@
         <v>11</v>
       </c>
       <c r="H148" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="I148" s="13" t="s">
-        <v>374</v>
-      </c>
+        <v>386</v>
+      </c>
+      <c r="I148" s="8"/>
     </row>
     <row r="149" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B149" t="s">
-        <v>377</v>
+        <v>387</v>
       </c>
       <c r="C149" t="s">
-        <v>75</v>
+        <v>387</v>
       </c>
       <c r="D149" s="5" t="s">
         <v>16</v>
@@ -5993,19 +5993,16 @@
         <v>11</v>
       </c>
       <c r="H149" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="I149" s="13"/>
+        <v>388</v>
+      </c>
+      <c r="I149" s="8"/>
     </row>
     <row r="150" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A150" t="s">
-        <v>378</v>
-      </c>
       <c r="B150" t="s">
-        <v>379</v>
+        <v>389</v>
       </c>
       <c r="C150" t="s">
-        <v>380</v>
+        <v>389</v>
       </c>
       <c r="D150" s="5" t="s">
         <v>16</v>
@@ -6020,16 +6017,16 @@
         <v>11</v>
       </c>
       <c r="H150" s="10" t="s">
-        <v>381</v>
+        <v>390</v>
       </c>
       <c r="I150" s="8"/>
     </row>
     <row r="151" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B151" t="s">
-        <v>382</v>
+        <v>391</v>
       </c>
       <c r="C151" t="s">
-        <v>383</v>
+        <v>391</v>
       </c>
       <c r="D151" s="5" t="s">
         <v>16</v>
@@ -6044,16 +6041,16 @@
         <v>11</v>
       </c>
       <c r="H151" s="10" t="s">
-        <v>384</v>
+        <v>392</v>
       </c>
       <c r="I151" s="8"/>
     </row>
     <row r="152" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B152" t="s">
-        <v>385</v>
+        <v>393</v>
       </c>
       <c r="C152" t="s">
-        <v>385</v>
+        <v>393</v>
       </c>
       <c r="D152" s="5" t="s">
         <v>16</v>
@@ -6068,16 +6065,16 @@
         <v>11</v>
       </c>
       <c r="H152" s="10" t="s">
-        <v>386</v>
+        <v>394</v>
       </c>
       <c r="I152" s="8"/>
     </row>
     <row r="153" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B153" t="s">
-        <v>387</v>
+        <v>395</v>
       </c>
       <c r="C153" t="s">
-        <v>387</v>
+        <v>395</v>
       </c>
       <c r="D153" s="5" t="s">
         <v>16</v>
@@ -6092,16 +6089,16 @@
         <v>11</v>
       </c>
       <c r="H153" s="10" t="s">
-        <v>388</v>
+        <v>396</v>
       </c>
       <c r="I153" s="8"/>
     </row>
     <row r="154" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B154" t="s">
-        <v>389</v>
+        <v>397</v>
       </c>
       <c r="C154" t="s">
-        <v>389</v>
+        <v>397</v>
       </c>
       <c r="D154" s="5" t="s">
         <v>16</v>
@@ -6116,16 +6113,16 @@
         <v>11</v>
       </c>
       <c r="H154" s="10" t="s">
-        <v>390</v>
+        <v>398</v>
       </c>
       <c r="I154" s="8"/>
     </row>
     <row r="155" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B155" t="s">
-        <v>391</v>
+        <v>399</v>
       </c>
       <c r="C155" t="s">
-        <v>391</v>
+        <v>399</v>
       </c>
       <c r="D155" s="5" t="s">
         <v>16</v>
@@ -6140,16 +6137,16 @@
         <v>11</v>
       </c>
       <c r="H155" s="10" t="s">
-        <v>392</v>
+        <v>400</v>
       </c>
       <c r="I155" s="8"/>
     </row>
     <row r="156" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B156" t="s">
-        <v>393</v>
+        <v>401</v>
       </c>
       <c r="C156" t="s">
-        <v>393</v>
+        <v>401</v>
       </c>
       <c r="D156" s="5" t="s">
         <v>16</v>
@@ -6164,16 +6161,16 @@
         <v>11</v>
       </c>
       <c r="H156" s="10" t="s">
-        <v>394</v>
+        <v>402</v>
       </c>
       <c r="I156" s="8"/>
     </row>
     <row r="157" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B157" t="s">
-        <v>395</v>
+        <v>403</v>
       </c>
       <c r="C157" t="s">
-        <v>395</v>
+        <v>403</v>
       </c>
       <c r="D157" s="5" t="s">
         <v>16</v>
@@ -6188,16 +6185,16 @@
         <v>11</v>
       </c>
       <c r="H157" s="10" t="s">
-        <v>396</v>
+        <v>404</v>
       </c>
       <c r="I157" s="8"/>
     </row>
     <row r="158" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B158" t="s">
-        <v>397</v>
+        <v>405</v>
       </c>
       <c r="C158" t="s">
-        <v>397</v>
+        <v>405</v>
       </c>
       <c r="D158" s="5" t="s">
         <v>16</v>
@@ -6212,16 +6209,16 @@
         <v>11</v>
       </c>
       <c r="H158" s="10" t="s">
-        <v>398</v>
+        <v>406</v>
       </c>
       <c r="I158" s="8"/>
     </row>
     <row r="159" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B159" t="s">
-        <v>399</v>
+        <v>407</v>
       </c>
       <c r="C159" t="s">
-        <v>399</v>
+        <v>407</v>
       </c>
       <c r="D159" s="5" t="s">
         <v>16</v>
@@ -6236,16 +6233,16 @@
         <v>11</v>
       </c>
       <c r="H159" s="10" t="s">
-        <v>400</v>
+        <v>408</v>
       </c>
       <c r="I159" s="8"/>
     </row>
     <row r="160" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B160" t="s">
-        <v>401</v>
+        <v>409</v>
       </c>
       <c r="C160" t="s">
-        <v>401</v>
+        <v>409</v>
       </c>
       <c r="D160" s="5" t="s">
         <v>16</v>
@@ -6260,16 +6257,16 @@
         <v>11</v>
       </c>
       <c r="H160" s="10" t="s">
-        <v>402</v>
+        <v>410</v>
       </c>
       <c r="I160" s="8"/>
     </row>
     <row r="161" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B161" t="s">
-        <v>403</v>
+        <v>411</v>
       </c>
       <c r="C161" t="s">
-        <v>403</v>
+        <v>411</v>
       </c>
       <c r="D161" s="5" t="s">
         <v>16</v>
@@ -6284,16 +6281,16 @@
         <v>11</v>
       </c>
       <c r="H161" s="10" t="s">
-        <v>404</v>
+        <v>412</v>
       </c>
       <c r="I161" s="8"/>
     </row>
     <row r="162" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B162" t="s">
-        <v>405</v>
+        <v>413</v>
       </c>
       <c r="C162" t="s">
-        <v>405</v>
+        <v>413</v>
       </c>
       <c r="D162" s="5" t="s">
         <v>16</v>
@@ -6308,16 +6305,16 @@
         <v>11</v>
       </c>
       <c r="H162" s="10" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
       <c r="I162" s="8"/>
     </row>
     <row r="163" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B163" t="s">
-        <v>407</v>
+        <v>415</v>
       </c>
       <c r="C163" t="s">
-        <v>407</v>
+        <v>415</v>
       </c>
       <c r="D163" s="5" t="s">
         <v>16</v>
@@ -6332,16 +6329,16 @@
         <v>11</v>
       </c>
       <c r="H163" s="10" t="s">
-        <v>408</v>
+        <v>416</v>
       </c>
       <c r="I163" s="8"/>
     </row>
     <row r="164" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B164" t="s">
-        <v>409</v>
+        <v>417</v>
       </c>
       <c r="C164" t="s">
-        <v>409</v>
+        <v>417</v>
       </c>
       <c r="D164" s="5" t="s">
         <v>16</v>
@@ -6356,16 +6353,16 @@
         <v>11</v>
       </c>
       <c r="H164" s="10" t="s">
-        <v>410</v>
+        <v>418</v>
       </c>
       <c r="I164" s="8"/>
     </row>
     <row r="165" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B165" t="s">
-        <v>411</v>
+        <v>419</v>
       </c>
       <c r="C165" t="s">
-        <v>411</v>
+        <v>419</v>
       </c>
       <c r="D165" s="5" t="s">
         <v>16</v>
@@ -6380,16 +6377,16 @@
         <v>11</v>
       </c>
       <c r="H165" s="10" t="s">
-        <v>412</v>
+        <v>420</v>
       </c>
       <c r="I165" s="8"/>
     </row>
     <row r="166" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B166" t="s">
-        <v>413</v>
+        <v>421</v>
       </c>
       <c r="C166" t="s">
-        <v>413</v>
+        <v>421</v>
       </c>
       <c r="D166" s="5" t="s">
         <v>16</v>
@@ -6404,16 +6401,16 @@
         <v>11</v>
       </c>
       <c r="H166" s="10" t="s">
-        <v>414</v>
+        <v>422</v>
       </c>
       <c r="I166" s="8"/>
     </row>
     <row r="167" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B167" t="s">
-        <v>415</v>
+        <v>423</v>
       </c>
       <c r="C167" t="s">
-        <v>415</v>
+        <v>423</v>
       </c>
       <c r="D167" s="5" t="s">
         <v>16</v>
@@ -6428,16 +6425,16 @@
         <v>11</v>
       </c>
       <c r="H167" s="10" t="s">
-        <v>416</v>
+        <v>424</v>
       </c>
       <c r="I167" s="8"/>
     </row>
     <row r="168" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B168" t="s">
-        <v>417</v>
+        <v>425</v>
       </c>
       <c r="C168" t="s">
-        <v>417</v>
+        <v>425</v>
       </c>
       <c r="D168" s="5" t="s">
         <v>16</v>
@@ -6452,16 +6449,16 @@
         <v>11</v>
       </c>
       <c r="H168" s="10" t="s">
-        <v>418</v>
+        <v>426</v>
       </c>
       <c r="I168" s="8"/>
     </row>
     <row r="169" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B169" t="s">
-        <v>419</v>
+        <v>427</v>
       </c>
       <c r="C169" t="s">
-        <v>419</v>
+        <v>427</v>
       </c>
       <c r="D169" s="5" t="s">
         <v>16</v>
@@ -6476,16 +6473,16 @@
         <v>11</v>
       </c>
       <c r="H169" s="10" t="s">
-        <v>420</v>
+        <v>428</v>
       </c>
       <c r="I169" s="8"/>
     </row>
     <row r="170" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B170" t="s">
-        <v>421</v>
+        <v>429</v>
       </c>
       <c r="C170" t="s">
-        <v>421</v>
+        <v>429</v>
       </c>
       <c r="D170" s="5" t="s">
         <v>16</v>
@@ -6500,16 +6497,16 @@
         <v>11</v>
       </c>
       <c r="H170" s="10" t="s">
-        <v>422</v>
+        <v>430</v>
       </c>
       <c r="I170" s="8"/>
     </row>
     <row r="171" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B171" t="s">
-        <v>423</v>
+        <v>431</v>
       </c>
       <c r="C171" t="s">
-        <v>423</v>
+        <v>431</v>
       </c>
       <c r="D171" s="5" t="s">
         <v>16</v>
@@ -6524,16 +6521,16 @@
         <v>11</v>
       </c>
       <c r="H171" s="10" t="s">
-        <v>424</v>
+        <v>432</v>
       </c>
       <c r="I171" s="8"/>
     </row>
     <row r="172" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B172" t="s">
-        <v>425</v>
+        <v>433</v>
       </c>
       <c r="C172" t="s">
-        <v>425</v>
+        <v>433</v>
       </c>
       <c r="D172" s="5" t="s">
         <v>16</v>
@@ -6548,16 +6545,16 @@
         <v>11</v>
       </c>
       <c r="H172" s="10" t="s">
-        <v>426</v>
+        <v>434</v>
       </c>
       <c r="I172" s="8"/>
     </row>
     <row r="173" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B173" t="s">
-        <v>427</v>
+        <v>435</v>
       </c>
       <c r="C173" t="s">
-        <v>427</v>
+        <v>435</v>
       </c>
       <c r="D173" s="5" t="s">
         <v>16</v>
@@ -6572,16 +6569,16 @@
         <v>11</v>
       </c>
       <c r="H173" s="10" t="s">
-        <v>428</v>
+        <v>436</v>
       </c>
       <c r="I173" s="8"/>
     </row>
     <row r="174" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B174" t="s">
-        <v>429</v>
+        <v>437</v>
       </c>
       <c r="C174" t="s">
-        <v>429</v>
+        <v>437</v>
       </c>
       <c r="D174" s="5" t="s">
         <v>16</v>
@@ -6596,16 +6593,16 @@
         <v>11</v>
       </c>
       <c r="H174" s="10" t="s">
-        <v>430</v>
+        <v>438</v>
       </c>
       <c r="I174" s="8"/>
     </row>
     <row r="175" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B175" t="s">
-        <v>431</v>
+        <v>439</v>
       </c>
       <c r="C175" t="s">
-        <v>431</v>
+        <v>439</v>
       </c>
       <c r="D175" s="5" t="s">
         <v>16</v>
@@ -6620,16 +6617,16 @@
         <v>11</v>
       </c>
       <c r="H175" s="10" t="s">
-        <v>432</v>
+        <v>440</v>
       </c>
       <c r="I175" s="8"/>
     </row>
     <row r="176" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B176" t="s">
-        <v>433</v>
+        <v>441</v>
       </c>
       <c r="C176" t="s">
-        <v>433</v>
+        <v>441</v>
       </c>
       <c r="D176" s="5" t="s">
         <v>16</v>
@@ -6644,16 +6641,16 @@
         <v>11</v>
       </c>
       <c r="H176" s="10" t="s">
-        <v>434</v>
+        <v>442</v>
       </c>
       <c r="I176" s="8"/>
     </row>
     <row r="177" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B177" t="s">
-        <v>435</v>
+        <v>443</v>
       </c>
       <c r="C177" t="s">
-        <v>435</v>
+        <v>443</v>
       </c>
       <c r="D177" s="5" t="s">
         <v>16</v>
@@ -6668,16 +6665,16 @@
         <v>11</v>
       </c>
       <c r="H177" s="10" t="s">
-        <v>436</v>
+        <v>444</v>
       </c>
       <c r="I177" s="8"/>
     </row>
     <row r="178" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B178" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="C178" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="D178" s="5" t="s">
         <v>16</v>
@@ -6692,16 +6689,16 @@
         <v>11</v>
       </c>
       <c r="H178" s="10" t="s">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="I178" s="8"/>
     </row>
     <row r="179" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B179" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
       <c r="C179" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
       <c r="D179" s="5" t="s">
         <v>16</v>
@@ -6716,16 +6713,16 @@
         <v>11</v>
       </c>
       <c r="H179" s="10" t="s">
-        <v>440</v>
+        <v>448</v>
       </c>
       <c r="I179" s="8"/>
     </row>
     <row r="180" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B180" t="s">
-        <v>441</v>
+        <v>449</v>
       </c>
       <c r="C180" t="s">
-        <v>441</v>
+        <v>449</v>
       </c>
       <c r="D180" s="5" t="s">
         <v>16</v>
@@ -6740,16 +6737,16 @@
         <v>11</v>
       </c>
       <c r="H180" s="10" t="s">
-        <v>442</v>
+        <v>450</v>
       </c>
       <c r="I180" s="8"/>
     </row>
     <row r="181" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B181" t="s">
-        <v>443</v>
+        <v>451</v>
       </c>
       <c r="C181" t="s">
-        <v>443</v>
+        <v>451</v>
       </c>
       <c r="D181" s="5" t="s">
         <v>16</v>
@@ -6764,16 +6761,16 @@
         <v>11</v>
       </c>
       <c r="H181" s="10" t="s">
-        <v>444</v>
+        <v>452</v>
       </c>
       <c r="I181" s="8"/>
     </row>
     <row r="182" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B182" t="s">
-        <v>445</v>
+        <v>453</v>
       </c>
       <c r="C182" t="s">
-        <v>445</v>
+        <v>453</v>
       </c>
       <c r="D182" s="5" t="s">
         <v>16</v>
@@ -6788,16 +6785,16 @@
         <v>11</v>
       </c>
       <c r="H182" s="10" t="s">
-        <v>446</v>
+        <v>454</v>
       </c>
       <c r="I182" s="8"/>
     </row>
     <row r="183" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B183" t="s">
-        <v>447</v>
+        <v>455</v>
       </c>
       <c r="C183" t="s">
-        <v>447</v>
+        <v>455</v>
       </c>
       <c r="D183" s="5" t="s">
         <v>16</v>
@@ -6812,16 +6809,16 @@
         <v>11</v>
       </c>
       <c r="H183" s="10" t="s">
-        <v>448</v>
+        <v>456</v>
       </c>
       <c r="I183" s="8"/>
     </row>
     <row r="184" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B184" t="s">
-        <v>449</v>
+        <v>457</v>
       </c>
       <c r="C184" t="s">
-        <v>449</v>
+        <v>457</v>
       </c>
       <c r="D184" s="5" t="s">
         <v>16</v>
@@ -6836,16 +6833,16 @@
         <v>11</v>
       </c>
       <c r="H184" s="10" t="s">
-        <v>450</v>
+        <v>458</v>
       </c>
       <c r="I184" s="8"/>
     </row>
     <row r="185" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B185" t="s">
-        <v>451</v>
+        <v>459</v>
       </c>
       <c r="C185" t="s">
-        <v>451</v>
+        <v>459</v>
       </c>
       <c r="D185" s="5" t="s">
         <v>16</v>
@@ -6860,16 +6857,16 @@
         <v>11</v>
       </c>
       <c r="H185" s="10" t="s">
-        <v>452</v>
+        <v>460</v>
       </c>
       <c r="I185" s="8"/>
     </row>
     <row r="186" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B186" t="s">
-        <v>453</v>
+        <v>461</v>
       </c>
       <c r="C186" t="s">
-        <v>453</v>
+        <v>461</v>
       </c>
       <c r="D186" s="5" t="s">
         <v>16</v>
@@ -6884,16 +6881,16 @@
         <v>11</v>
       </c>
       <c r="H186" s="10" t="s">
-        <v>454</v>
+        <v>462</v>
       </c>
       <c r="I186" s="8"/>
     </row>
     <row r="187" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B187" t="s">
-        <v>455</v>
+        <v>463</v>
       </c>
       <c r="C187" t="s">
-        <v>455</v>
+        <v>463</v>
       </c>
       <c r="D187" s="5" t="s">
         <v>16</v>
@@ -6904,44 +6901,45 @@
       <c r="F187" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G187" s="8" t="s">
-        <v>11</v>
-      </c>
+      <c r="G187" s="8"/>
       <c r="H187" s="10" t="s">
-        <v>456</v>
+        <v>464</v>
       </c>
       <c r="I187" s="8"/>
     </row>
     <row r="188" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A188" t="s">
+        <v>465</v>
+      </c>
       <c r="B188" t="s">
-        <v>457</v>
+        <v>466</v>
       </c>
       <c r="C188" t="s">
-        <v>457</v>
+        <v>466</v>
       </c>
       <c r="D188" s="5" t="s">
         <v>16</v>
       </c>
       <c r="E188" s="5" t="s">
-        <v>16</v>
+        <v>466</v>
       </c>
       <c r="F188" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="G188" s="8" t="s">
-        <v>11</v>
-      </c>
+        <v>466</v>
+      </c>
+      <c r="G188" s="8"/>
       <c r="H188" s="10" t="s">
-        <v>458</v>
-      </c>
-      <c r="I188" s="8"/>
+        <v>16</v>
+      </c>
+      <c r="I188" s="13" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="189" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B189" t="s">
-        <v>459</v>
+        <v>467</v>
       </c>
       <c r="C189" t="s">
-        <v>459</v>
+        <v>467</v>
       </c>
       <c r="D189" s="5" t="s">
         <v>16</v>
@@ -6952,44 +6950,44 @@
       <c r="F189" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G189" s="8" t="s">
-        <v>11</v>
-      </c>
+      <c r="G189" s="8"/>
       <c r="H189" s="10" t="s">
-        <v>460</v>
-      </c>
-      <c r="I189" s="8"/>
+        <v>16</v>
+      </c>
+      <c r="I189" s="13" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="190" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B190" t="s">
-        <v>461</v>
+        <v>468</v>
       </c>
       <c r="C190" t="s">
-        <v>461</v>
+        <v>468</v>
       </c>
       <c r="D190" s="5" t="s">
-        <v>16</v>
+        <v>469</v>
       </c>
       <c r="E190" s="5" t="s">
-        <v>16</v>
+        <v>470</v>
       </c>
       <c r="F190" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G190" s="8" t="s">
-        <v>11</v>
-      </c>
+      <c r="G190" s="8"/>
       <c r="H190" s="10" t="s">
-        <v>462</v>
-      </c>
-      <c r="I190" s="8"/>
+        <v>16</v>
+      </c>
+      <c r="I190" s="13" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="191" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B191" t="s">
-        <v>463</v>
+        <v>62</v>
       </c>
       <c r="C191" t="s">
-        <v>463</v>
+        <v>62</v>
       </c>
       <c r="D191" s="5" t="s">
         <v>16</v>
@@ -7002,28 +7000,27 @@
       </c>
       <c r="G191" s="8"/>
       <c r="H191" s="10" t="s">
-        <v>464</v>
-      </c>
-      <c r="I191" s="8"/>
+        <v>16</v>
+      </c>
+      <c r="I191" s="13" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="192" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A192" t="s">
-        <v>465</v>
-      </c>
       <c r="B192" t="s">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="C192" t="s">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="D192" s="5" t="s">
         <v>16</v>
       </c>
       <c r="E192" s="5" t="s">
-        <v>466</v>
+        <v>16</v>
       </c>
       <c r="F192" s="5" t="s">
-        <v>466</v>
+        <v>16</v>
       </c>
       <c r="G192" s="8"/>
       <c r="H192" s="10" t="s">
@@ -7033,12 +7030,12 @@
         <v>16</v>
       </c>
     </row>
-    <row r="193" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B193" t="s">
-        <v>467</v>
+        <v>369</v>
       </c>
       <c r="C193" t="s">
-        <v>467</v>
+        <v>369</v>
       </c>
       <c r="D193" s="5" t="s">
         <v>16</v>
@@ -7057,117 +7054,133 @@
         <v>16</v>
       </c>
     </row>
-    <row r="194" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="B194" t="s">
-        <v>468</v>
-      </c>
-      <c r="C194" t="s">
-        <v>468</v>
-      </c>
-      <c r="D194" s="5" t="s">
-        <v>469</v>
-      </c>
-      <c r="E194" s="5" t="s">
-        <v>470</v>
-      </c>
-      <c r="F194" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="G194" s="8"/>
+    <row r="194" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A194" s="4"/>
+      <c r="B194" s="4" t="s">
+        <v>472</v>
+      </c>
+      <c r="C194" s="4" t="s">
+        <v>472</v>
+      </c>
+      <c r="D194" s="3" t="s">
+        <v>472</v>
+      </c>
+      <c r="E194" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F194" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G194" s="8" t="s">
+        <v>473</v>
+      </c>
       <c r="H194" s="10" t="s">
         <v>16</v>
       </c>
       <c r="I194" s="13" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="195" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="B195" t="s">
-        <v>62</v>
-      </c>
-      <c r="C195" t="s">
-        <v>62</v>
-      </c>
-      <c r="D195" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="E195" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="F195" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="G195" s="8"/>
+      <c r="J194" s="4"/>
+    </row>
+    <row r="195" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A195" s="4"/>
+      <c r="B195" s="4" t="s">
+        <v>474</v>
+      </c>
+      <c r="C195" s="4" t="s">
+        <v>474</v>
+      </c>
+      <c r="D195" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E195" s="3" t="s">
+        <v>474</v>
+      </c>
+      <c r="F195" s="3" t="s">
+        <v>474</v>
+      </c>
+      <c r="G195" s="8" t="s">
+        <v>473</v>
+      </c>
       <c r="H195" s="10" t="s">
         <v>16</v>
       </c>
       <c r="I195" s="13" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="196" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="B196" t="s">
-        <v>471</v>
-      </c>
-      <c r="C196" t="s">
-        <v>471</v>
-      </c>
-      <c r="D196" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="E196" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="F196" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="G196" s="8"/>
+      <c r="J195" s="4"/>
+    </row>
+    <row r="196" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A196" s="4"/>
+      <c r="B196" s="4" t="s">
+        <v>337</v>
+      </c>
+      <c r="C196" s="4" t="s">
+        <v>337</v>
+      </c>
+      <c r="D196" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="E196" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F196" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G196" s="8" t="s">
+        <v>473</v>
+      </c>
       <c r="H196" s="10" t="s">
         <v>16</v>
       </c>
       <c r="I196" s="13" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="197" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="B197" t="s">
-        <v>369</v>
-      </c>
-      <c r="C197" t="s">
-        <v>369</v>
-      </c>
-      <c r="D197" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="E197" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="F197" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="G197" s="8"/>
+      <c r="J196" s="4"/>
+    </row>
+    <row r="197" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A197" s="4"/>
+      <c r="B197" s="4" t="s">
+        <v>475</v>
+      </c>
+      <c r="C197" s="4" t="s">
+        <v>475</v>
+      </c>
+      <c r="D197" s="3" t="s">
+        <v>475</v>
+      </c>
+      <c r="E197" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F197" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G197" s="8" t="s">
+        <v>473</v>
+      </c>
       <c r="H197" s="10" t="s">
         <v>16</v>
       </c>
       <c r="I197" s="13" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="198" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="J197" s="4"/>
+    </row>
+    <row r="198" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B198" s="4" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="C198" s="4" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="D198" s="3" t="s">
-        <v>472</v>
+        <v>16</v>
       </c>
       <c r="E198" s="3" t="s">
-        <v>16</v>
+        <v>476</v>
       </c>
       <c r="F198" s="3" t="s">
-        <v>16</v>
+        <v>476</v>
       </c>
       <c r="G198" s="8" t="s">
         <v>473</v>
@@ -7179,201 +7192,108 @@
         <v>16</v>
       </c>
     </row>
-    <row r="199" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B199" s="4" t="s">
-        <v>474</v>
-      </c>
-      <c r="C199" s="4" t="s">
-        <v>474</v>
-      </c>
-      <c r="D199" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E199" s="3" t="s">
-        <v>474</v>
-      </c>
-      <c r="F199" s="3" t="s">
-        <v>474</v>
-      </c>
-      <c r="G199" s="8" t="s">
-        <v>473</v>
-      </c>
+    <row r="199" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A199" t="s">
+        <v>477</v>
+      </c>
+      <c r="B199" t="s">
+        <v>478</v>
+      </c>
+      <c r="C199" t="s">
+        <v>478</v>
+      </c>
+      <c r="D199" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="E199" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F199" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G199" s="8"/>
       <c r="H199" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="I199" s="13" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="200" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B200" s="4" t="s">
-        <v>337</v>
-      </c>
-      <c r="C200" s="4" t="s">
-        <v>337</v>
-      </c>
-      <c r="D200" s="3" t="s">
-        <v>337</v>
-      </c>
-      <c r="E200" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="F200" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G200" s="8" t="s">
-        <v>473</v>
-      </c>
+        <v>479</v>
+      </c>
+      <c r="I199" s="8"/>
+      <c r="J199"/>
+    </row>
+    <row r="200" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A200"/>
+      <c r="B200" t="s">
+        <v>480</v>
+      </c>
+      <c r="C200" t="s">
+        <v>480</v>
+      </c>
+      <c r="D200" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="E200" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F200" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G200" s="8"/>
       <c r="H200" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="I200" s="13" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="201" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B201" s="4" t="s">
-        <v>475</v>
-      </c>
-      <c r="C201" s="4" t="s">
-        <v>475</v>
-      </c>
-      <c r="D201" s="3" t="s">
-        <v>475</v>
-      </c>
-      <c r="E201" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="F201" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G201" s="8" t="s">
-        <v>473</v>
-      </c>
+        <v>481</v>
+      </c>
+      <c r="I200" s="8"/>
+      <c r="J200"/>
+    </row>
+    <row r="201" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A201"/>
+      <c r="B201" t="s">
+        <v>482</v>
+      </c>
+      <c r="C201" t="s">
+        <v>482</v>
+      </c>
+      <c r="D201" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="E201" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F201" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G201" s="8"/>
       <c r="H201" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="I201" s="13" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="202" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B202" s="4" t="s">
-        <v>476</v>
-      </c>
-      <c r="C202" s="4" t="s">
-        <v>476</v>
-      </c>
-      <c r="D202" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E202" s="3" t="s">
-        <v>476</v>
-      </c>
-      <c r="F202" s="3" t="s">
-        <v>476</v>
-      </c>
-      <c r="G202" s="8" t="s">
-        <v>473</v>
-      </c>
+        <v>483</v>
+      </c>
+      <c r="I201" s="8"/>
+      <c r="J201"/>
+    </row>
+    <row r="202" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A202"/>
+      <c r="B202" t="s">
+        <v>484</v>
+      </c>
+      <c r="C202" t="s">
+        <v>484</v>
+      </c>
+      <c r="D202" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="E202" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F202" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G202" s="8"/>
       <c r="H202" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="I202" s="13" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="203" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A203" t="s">
-        <v>477</v>
-      </c>
-      <c r="B203" t="s">
-        <v>478</v>
-      </c>
-      <c r="C203" t="s">
-        <v>478</v>
-      </c>
-      <c r="D203" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="E203" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="F203" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="G203" s="8"/>
-      <c r="H203" s="10" t="s">
-        <v>479</v>
-      </c>
-      <c r="I203" s="8"/>
-    </row>
-    <row r="204" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="B204" t="s">
-        <v>480</v>
-      </c>
-      <c r="C204" t="s">
-        <v>480</v>
-      </c>
-      <c r="D204" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="E204" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="F204" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="G204" s="8"/>
-      <c r="H204" s="10" t="s">
-        <v>481</v>
-      </c>
-      <c r="I204" s="8"/>
-    </row>
-    <row r="205" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="B205" t="s">
-        <v>482</v>
-      </c>
-      <c r="C205" t="s">
-        <v>482</v>
-      </c>
-      <c r="D205" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="E205" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="F205" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="G205" s="8"/>
-      <c r="H205" s="10" t="s">
-        <v>483</v>
-      </c>
-      <c r="I205" s="8"/>
-    </row>
-    <row r="206" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="B206" t="s">
-        <v>484</v>
-      </c>
-      <c r="C206" t="s">
-        <v>484</v>
-      </c>
-      <c r="D206" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="E206" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="F206" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="G206" s="8"/>
-      <c r="H206" s="10" t="s">
         <v>485</v>
       </c>
-      <c r="I206" s="8"/>
-    </row>
+      <c r="I202" s="8"/>
+      <c r="J202"/>
+    </row>
+    <row r="203" spans="1:10" x14ac:dyDescent="0.2"/>
+    <row r="204" spans="1:10" x14ac:dyDescent="0.2"/>
+    <row r="205" spans="1:10" x14ac:dyDescent="0.2"/>
+    <row r="206" spans="1:10" x14ac:dyDescent="0.2"/>
   </sheetData>
   <autoFilter ref="A1:I206" xr:uid="{89DF070F-E429-4D58-AA77-4A646FC37142}"/>
   <hyperlinks>
@@ -11683,7 +11603,7 @@
       </c>
       <c r="C3">
         <f>MATCH(B3,Lookup!D:D,0)</f>
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D3" t="s">
         <v>501</v>
@@ -11693,7 +11613,7 @@
       </c>
       <c r="F3">
         <f>MATCH(E3,Lookup!E:E,0)</f>
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G3" t="s">
         <v>502</v>
@@ -11703,7 +11623,7 @@
       </c>
       <c r="I3">
         <f>MATCH(H3,Lookup!F:F,0)</f>
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
@@ -11715,7 +11635,7 @@
       </c>
       <c r="C4">
         <f>MATCH(B4,Lookup!D:D,0)</f>
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D4" t="s">
         <v>501</v>
@@ -11725,7 +11645,7 @@
       </c>
       <c r="F4">
         <f>MATCH(E4,Lookup!E:E,0)</f>
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G4" t="s">
         <v>502</v>
@@ -11735,7 +11655,7 @@
       </c>
       <c r="I4">
         <f>MATCH(H4,Lookup!F:F,0)</f>
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.2">
@@ -11747,7 +11667,7 @@
       </c>
       <c r="C5">
         <f>MATCH(B5,Lookup!D:D,0)</f>
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="D5" t="s">
         <v>501</v>
@@ -11757,7 +11677,7 @@
       </c>
       <c r="F5">
         <f>MATCH(E5,Lookup!E:E,0)</f>
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="G5" t="s">
         <v>502</v>
@@ -11767,7 +11687,7 @@
       </c>
       <c r="I5">
         <f>MATCH(H5,Lookup!F:F,0)</f>
-        <v>101</v>
+        <v>97</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.2">
@@ -11779,7 +11699,7 @@
       </c>
       <c r="C6">
         <f>MATCH(B6,Lookup!D:D,0)</f>
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="D6" t="s">
         <v>501</v>
@@ -11789,7 +11709,7 @@
       </c>
       <c r="F6">
         <f>MATCH(E6,Lookup!E:E,0)</f>
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="G6" t="s">
         <v>502</v>
@@ -11799,7 +11719,7 @@
       </c>
       <c r="I6">
         <f>MATCH(H6,Lookup!F:F,0)</f>
-        <v>102</v>
+        <v>98</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.2">
@@ -11811,7 +11731,7 @@
       </c>
       <c r="C7">
         <f>MATCH(B7,Lookup!D:D,0)</f>
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D7" t="s">
         <v>501</v>
@@ -11821,7 +11741,7 @@
       </c>
       <c r="F7">
         <f>MATCH(E7,Lookup!E:E,0)</f>
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G7" t="s">
         <v>502</v>
@@ -11831,7 +11751,7 @@
       </c>
       <c r="I7">
         <f>MATCH(H7,Lookup!F:F,0)</f>
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.2">
@@ -11843,7 +11763,7 @@
       </c>
       <c r="C8">
         <f>MATCH(B8,Lookup!D:D,0)</f>
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D8" t="s">
         <v>501</v>
@@ -11853,7 +11773,7 @@
       </c>
       <c r="F8">
         <f>MATCH(E8,Lookup!E:E,0)</f>
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G8" t="s">
         <v>502</v>
@@ -11863,7 +11783,7 @@
       </c>
       <c r="I8">
         <f>MATCH(H8,Lookup!F:F,0)</f>
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.2">
@@ -11917,7 +11837,7 @@
       </c>
       <c r="F10">
         <f>MATCH(E10,Lookup!E:E,0)</f>
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G10" t="s">
         <v>502</v>
@@ -11927,7 +11847,7 @@
       </c>
       <c r="I10">
         <f>MATCH(H10,Lookup!F:F,0)</f>
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.2">
@@ -11949,7 +11869,7 @@
       </c>
       <c r="F11">
         <f>MATCH(E11,Lookup!E:E,0)</f>
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G11" t="s">
         <v>502</v>
@@ -11959,7 +11879,7 @@
       </c>
       <c r="I11">
         <f>MATCH(H11,Lookup!F:F,0)</f>
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.2">
@@ -11981,7 +11901,7 @@
       </c>
       <c r="F12">
         <f>MATCH(E12,Lookup!E:E,0)</f>
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="G12" t="s">
         <v>502</v>
@@ -11991,7 +11911,7 @@
       </c>
       <c r="I12">
         <f>MATCH(H12,Lookup!F:F,0)</f>
-        <v>192</v>
+        <v>188</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.2">
@@ -12003,7 +11923,7 @@
       </c>
       <c r="C13">
         <f>MATCH(B13,Lookup!D:D,0)</f>
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="D13" t="s">
         <v>501</v>
@@ -12035,7 +11955,7 @@
       </c>
       <c r="C14">
         <f>MATCH(B14,Lookup!D:D,0)</f>
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D14" t="s">
         <v>501</v>
@@ -12067,7 +11987,7 @@
       </c>
       <c r="C15">
         <f>MATCH(B15,Lookup!D:D,0)</f>
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D15" t="s">
         <v>501</v>
@@ -12099,7 +12019,7 @@
       </c>
       <c r="C16">
         <f>MATCH(B16,Lookup!D:D,0)</f>
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="D16" t="s">
         <v>501</v>
@@ -12109,7 +12029,7 @@
       </c>
       <c r="F16">
         <f>MATCH(E16,Lookup!E:E,0)</f>
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="G16" t="s">
         <v>502</v>
@@ -12119,7 +12039,7 @@
       </c>
       <c r="I16">
         <f>MATCH(H16,Lookup!F:F,0)</f>
-        <v>100</v>
+        <v>96</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.2">
@@ -12131,7 +12051,7 @@
       </c>
       <c r="C17">
         <f>MATCH(B17,Lookup!D:D,0)</f>
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="D17" t="s">
         <v>501</v>
@@ -12141,7 +12061,7 @@
       </c>
       <c r="F17">
         <f>MATCH(E17,Lookup!E:E,0)</f>
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G17" t="s">
         <v>502</v>
@@ -12151,7 +12071,7 @@
       </c>
       <c r="I17">
         <f>MATCH(H17,Lookup!F:F,0)</f>
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.2">
@@ -12163,7 +12083,7 @@
       </c>
       <c r="C18">
         <f>MATCH(B18,Lookup!D:D,0)</f>
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="D18" t="s">
         <v>501</v>
@@ -12173,7 +12093,7 @@
       </c>
       <c r="F18">
         <f>MATCH(E18,Lookup!E:E,0)</f>
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G18" t="s">
         <v>502</v>
@@ -12183,7 +12103,7 @@
       </c>
       <c r="I18">
         <f>MATCH(H18,Lookup!F:F,0)</f>
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.2">
@@ -12195,7 +12115,7 @@
       </c>
       <c r="C19">
         <f>MATCH(B19,Lookup!D:D,0)</f>
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="D19" t="s">
         <v>501</v>
@@ -12205,7 +12125,7 @@
       </c>
       <c r="F19">
         <f>MATCH(E19,Lookup!E:E,0)</f>
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G19" t="s">
         <v>502</v>
@@ -12215,7 +12135,7 @@
       </c>
       <c r="I19">
         <f>MATCH(H19,Lookup!F:F,0)</f>
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.2">
@@ -12227,7 +12147,7 @@
       </c>
       <c r="C20">
         <f>MATCH(B20,Lookup!D:D,0)</f>
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="D20" t="s">
         <v>501</v>
@@ -12237,7 +12157,7 @@
       </c>
       <c r="F20">
         <f>MATCH(E20,Lookup!E:E,0)</f>
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="G20" t="s">
         <v>502</v>
@@ -12247,7 +12167,7 @@
       </c>
       <c r="I20">
         <f>MATCH(H20,Lookup!F:F,0)</f>
-        <v>135</v>
+        <v>131</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.2">
@@ -12259,7 +12179,7 @@
       </c>
       <c r="C21">
         <f>MATCH(B21,Lookup!D:D,0)</f>
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="D21" t="s">
         <v>501</v>
@@ -12291,7 +12211,7 @@
       </c>
       <c r="C22">
         <f>MATCH(B22,Lookup!D:D,0)</f>
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="D22" t="s">
         <v>501</v>
@@ -12301,7 +12221,7 @@
       </c>
       <c r="F22">
         <f>MATCH(E22,Lookup!E:E,0)</f>
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="G22" t="s">
         <v>502</v>
@@ -12323,7 +12243,7 @@
       </c>
       <c r="C23">
         <f>MATCH(B23,Lookup!D:D,0)</f>
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="D23" t="s">
         <v>501</v>
@@ -12355,7 +12275,7 @@
       </c>
       <c r="C24">
         <f>MATCH(B24,Lookup!D:D,0)</f>
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D24" t="s">
         <v>501</v>
@@ -12365,7 +12285,7 @@
       </c>
       <c r="F24">
         <f>MATCH(E24,Lookup!E:E,0)</f>
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="G24" t="s">
         <v>502</v>
@@ -12387,7 +12307,7 @@
       </c>
       <c r="C25">
         <f>MATCH(B25,Lookup!D:D,0)</f>
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="D25" t="s">
         <v>501</v>
@@ -12407,7 +12327,7 @@
       </c>
       <c r="I25">
         <f>MATCH(H25,Lookup!F:F,0)</f>
-        <v>136</v>
+        <v>132</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.2">
@@ -12419,7 +12339,7 @@
       </c>
       <c r="C26">
         <f>MATCH(B26,Lookup!D:D,0)</f>
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="D26" t="s">
         <v>501</v>
@@ -12451,7 +12371,7 @@
       </c>
       <c r="C27">
         <f>MATCH(B27,Lookup!D:D,0)</f>
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="D27" t="s">
         <v>501</v>
@@ -12461,7 +12381,7 @@
       </c>
       <c r="F27">
         <f>MATCH(E27,Lookup!E:E,0)</f>
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="G27" t="s">
         <v>502</v>
@@ -12483,7 +12403,7 @@
       </c>
       <c r="C28">
         <f>MATCH(B28,Lookup!D:D,0)</f>
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="D28" t="s">
         <v>501</v>
@@ -12503,7 +12423,7 @@
       </c>
       <c r="I28">
         <f>MATCH(H28,Lookup!F:F,0)</f>
-        <v>202</v>
+        <v>198</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.2">
@@ -12537,7 +12457,7 @@
       </c>
       <c r="F30">
         <f>MATCH(E30,Lookup!E:E,0)</f>
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="G30" t="s">
         <v>502</v>
@@ -12591,7 +12511,7 @@
       </c>
       <c r="I32">
         <f>MATCH(H32,Lookup!F:F,0)</f>
-        <v>111</v>
+        <v>107</v>
       </c>
     </row>
     <row r="33" spans="4:9" x14ac:dyDescent="0.2">
@@ -12613,7 +12533,7 @@
       </c>
       <c r="I33">
         <f>MATCH(H33,Lookup!F:F,0)</f>
-        <v>112</v>
+        <v>108</v>
       </c>
     </row>
     <row r="34" spans="4:9" x14ac:dyDescent="0.2">
@@ -12625,7 +12545,7 @@
       </c>
       <c r="F34">
         <f>MATCH(E34,Lookup!E:E,0)</f>
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="G34" t="s">
         <v>502</v>
@@ -12635,7 +12555,7 @@
       </c>
       <c r="I34">
         <f>MATCH(H34,Lookup!F:F,0)</f>
-        <v>114</v>
+        <v>110</v>
       </c>
     </row>
     <row r="35" spans="4:9" x14ac:dyDescent="0.2">
@@ -12647,7 +12567,7 @@
       </c>
       <c r="F35">
         <f>MATCH(E35,Lookup!E:E,0)</f>
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="G35" t="s">
         <v>502</v>
@@ -12657,7 +12577,7 @@
       </c>
       <c r="I35">
         <f>MATCH(H35,Lookup!F:F,0)</f>
-        <v>115</v>
+        <v>111</v>
       </c>
     </row>
     <row r="36" spans="4:9" x14ac:dyDescent="0.2">
@@ -12669,7 +12589,7 @@
       </c>
       <c r="F36">
         <f>MATCH(E36,Lookup!E:E,0)</f>
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="G36" t="s">
         <v>502</v>
@@ -12679,7 +12599,7 @@
       </c>
       <c r="I36">
         <f>MATCH(H36,Lookup!F:F,0)</f>
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="37" spans="4:9" x14ac:dyDescent="0.2">
@@ -12691,7 +12611,7 @@
       </c>
       <c r="F37">
         <f>MATCH(E37,Lookup!E:E,0)</f>
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G37" t="s">
         <v>502</v>
@@ -12701,7 +12621,7 @@
       </c>
       <c r="I37">
         <f>MATCH(H37,Lookup!F:F,0)</f>
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="38" spans="4:9" x14ac:dyDescent="0.2">
@@ -12713,7 +12633,7 @@
       </c>
       <c r="F38">
         <f>MATCH(E38,Lookup!E:E,0)</f>
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G38" t="s">
         <v>502</v>
@@ -12745,7 +12665,7 @@
       </c>
       <c r="I39">
         <f>MATCH(H39,Lookup!F:F,0)</f>
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="40" spans="4:9" x14ac:dyDescent="0.2">
@@ -12757,7 +12677,7 @@
       </c>
       <c r="F40">
         <f>MATCH(E40,Lookup!E:E,0)</f>
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G40" t="s">
         <v>502</v>
@@ -12789,7 +12709,7 @@
       </c>
       <c r="I41">
         <f>MATCH(H41,Lookup!F:F,0)</f>
-        <v>126</v>
+        <v>122</v>
       </c>
     </row>
     <row r="42" spans="4:9" x14ac:dyDescent="0.2">
@@ -12801,7 +12721,7 @@
       </c>
       <c r="F42">
         <f>MATCH(E42,Lookup!E:E,0)</f>
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="G42" t="s">
         <v>502</v>
@@ -12811,7 +12731,7 @@
       </c>
       <c r="I42">
         <f>MATCH(H42,Lookup!F:F,0)</f>
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="43" spans="4:9" x14ac:dyDescent="0.2">
@@ -12823,7 +12743,7 @@
       </c>
       <c r="F43">
         <f>MATCH(E43,Lookup!E:E,0)</f>
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G43" t="s">
         <v>502</v>
@@ -12833,7 +12753,7 @@
       </c>
       <c r="I43">
         <f>MATCH(H43,Lookup!F:F,0)</f>
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="44" spans="4:9" x14ac:dyDescent="0.2">
@@ -12845,7 +12765,7 @@
       </c>
       <c r="F44">
         <f>MATCH(E44,Lookup!E:E,0)</f>
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G44" t="s">
         <v>502</v>
@@ -12855,7 +12775,7 @@
       </c>
       <c r="I44">
         <f>MATCH(H44,Lookup!F:F,0)</f>
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="45" spans="4:9" x14ac:dyDescent="0.2">
@@ -12867,7 +12787,7 @@
       </c>
       <c r="F45">
         <f>MATCH(E45,Lookup!E:E,0)</f>
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G45" t="s">
         <v>502</v>
@@ -12877,7 +12797,7 @@
       </c>
       <c r="I45">
         <f>MATCH(H45,Lookup!F:F,0)</f>
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="46" spans="4:9" x14ac:dyDescent="0.2">
@@ -12889,7 +12809,7 @@
       </c>
       <c r="F46">
         <f>MATCH(E46,Lookup!E:E,0)</f>
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="G46" t="s">
         <v>502</v>
@@ -12899,7 +12819,7 @@
       </c>
       <c r="I46">
         <f>MATCH(H46,Lookup!F:F,0)</f>
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="47" spans="4:9" x14ac:dyDescent="0.2">
@@ -12911,7 +12831,7 @@
       </c>
       <c r="F47">
         <f>MATCH(E47,Lookup!E:E,0)</f>
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G47" t="s">
         <v>502</v>
@@ -12921,7 +12841,7 @@
       </c>
       <c r="I47">
         <f>MATCH(H47,Lookup!F:F,0)</f>
-        <v>117</v>
+        <v>113</v>
       </c>
     </row>
     <row r="48" spans="4:9" x14ac:dyDescent="0.2">
@@ -12933,7 +12853,7 @@
       </c>
       <c r="F48">
         <f>MATCH(E48,Lookup!E:E,0)</f>
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G48" t="s">
         <v>502</v>
@@ -12943,7 +12863,7 @@
       </c>
       <c r="I48">
         <f>MATCH(H48,Lookup!F:F,0)</f>
-        <v>120</v>
+        <v>116</v>
       </c>
     </row>
     <row r="49" spans="4:9" x14ac:dyDescent="0.2">
@@ -12955,7 +12875,7 @@
       </c>
       <c r="F49">
         <f>MATCH(E49,Lookup!E:E,0)</f>
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="G49" t="s">
         <v>502</v>
@@ -12965,7 +12885,7 @@
       </c>
       <c r="I49">
         <f>MATCH(H49,Lookup!F:F,0)</f>
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="50" spans="4:9" x14ac:dyDescent="0.2">
@@ -12977,7 +12897,7 @@
       </c>
       <c r="F50">
         <f>MATCH(E50,Lookup!E:E,0)</f>
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="G50" t="s">
         <v>502</v>
@@ -12987,7 +12907,7 @@
       </c>
       <c r="I50">
         <f>MATCH(H50,Lookup!F:F,0)</f>
-        <v>110</v>
+        <v>106</v>
       </c>
     </row>
     <row r="51" spans="4:9" x14ac:dyDescent="0.2">
@@ -12999,7 +12919,7 @@
       </c>
       <c r="F51">
         <f>MATCH(E51,Lookup!E:E,0)</f>
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G51" t="s">
         <v>502</v>
@@ -13009,7 +12929,7 @@
       </c>
       <c r="I51">
         <f>MATCH(H51,Lookup!F:F,0)</f>
-        <v>118</v>
+        <v>114</v>
       </c>
     </row>
     <row r="52" spans="4:9" x14ac:dyDescent="0.2">
@@ -13021,7 +12941,7 @@
       </c>
       <c r="F52">
         <f>MATCH(E52,Lookup!E:E,0)</f>
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="G52" t="s">
         <v>502</v>
@@ -13031,7 +12951,7 @@
       </c>
       <c r="I52">
         <f>MATCH(H52,Lookup!F:F,0)</f>
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="53" spans="4:9" x14ac:dyDescent="0.2">
@@ -13043,7 +12963,7 @@
       </c>
       <c r="F53">
         <f>MATCH(E53,Lookup!E:E,0)</f>
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="G53" t="s">
         <v>502</v>
@@ -13053,7 +12973,7 @@
       </c>
       <c r="I53">
         <f>MATCH(H53,Lookup!F:F,0)</f>
-        <v>139</v>
+        <v>135</v>
       </c>
     </row>
     <row r="54" spans="4:9" x14ac:dyDescent="0.2">
@@ -13065,7 +12985,7 @@
       </c>
       <c r="F54">
         <f>MATCH(E54,Lookup!E:E,0)</f>
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G54" t="s">
         <v>502</v>
@@ -13075,7 +12995,7 @@
       </c>
       <c r="I54">
         <f>MATCH(H54,Lookup!F:F,0)</f>
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="55" spans="4:9" x14ac:dyDescent="0.2">
@@ -13087,7 +13007,7 @@
       </c>
       <c r="F55">
         <f>MATCH(E55,Lookup!E:E,0)</f>
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="G55" t="s">
         <v>502</v>
@@ -13097,7 +13017,7 @@
       </c>
       <c r="I55">
         <f>MATCH(H55,Lookup!F:F,0)</f>
-        <v>143</v>
+        <v>139</v>
       </c>
     </row>
     <row r="56" spans="4:9" x14ac:dyDescent="0.2">
@@ -13109,7 +13029,7 @@
       </c>
       <c r="F56">
         <f>MATCH(E56,Lookup!E:E,0)</f>
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G56" t="s">
         <v>502</v>
@@ -13119,7 +13039,7 @@
       </c>
       <c r="I56">
         <f>MATCH(H56,Lookup!F:F,0)</f>
-        <v>142</v>
+        <v>138</v>
       </c>
     </row>
     <row r="57" spans="4:9" x14ac:dyDescent="0.2">
@@ -13131,7 +13051,7 @@
       </c>
       <c r="F57">
         <f>MATCH(E57,Lookup!E:E,0)</f>
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="G57" t="s">
         <v>502</v>
@@ -13141,7 +13061,7 @@
       </c>
       <c r="I57">
         <f>MATCH(H57,Lookup!F:F,0)</f>
-        <v>199</v>
+        <v>195</v>
       </c>
     </row>
     <row r="58" spans="4:9" x14ac:dyDescent="0.2">
@@ -13153,7 +13073,7 @@
       </c>
       <c r="F58">
         <f>MATCH(E58,Lookup!E:E,0)</f>
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="G58" t="s">
         <v>502</v>
@@ -13163,7 +13083,7 @@
       </c>
       <c r="I58">
         <f>MATCH(H58,Lookup!F:F,0)</f>
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="59" spans="4:9" x14ac:dyDescent="0.2">
@@ -13175,7 +13095,7 @@
       </c>
       <c r="F59">
         <f>MATCH(E59,Lookup!E:E,0)</f>
-        <v>199</v>
+        <v>195</v>
       </c>
     </row>
     <row r="60" spans="4:9" x14ac:dyDescent="0.2">
@@ -13187,7 +13107,7 @@
       </c>
       <c r="F60">
         <f>MATCH(E60,Lookup!E:E,0)</f>
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
   </sheetData>
@@ -14327,6 +14247,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100B674EA4B021E7B4197E0B77DCF8770A8" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ebb401e81e3712a12d23a789d2bfa9fe">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f1c51713-a7b9-4899-a01c-db85572982cc" xmlns:ns3="3ac97f74-887d-4038-a207-790912953edc" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="3a6713f0e65e3bfee893efc160aaadb3" ns2:_="" ns3:_="">
     <xsd:import namespace="f1c51713-a7b9-4899-a01c-db85572982cc"/>
@@ -14533,15 +14462,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A53362A7-9112-4B9B-A76B-23EB85896A3D}">
   <ds:schemaRefs>
@@ -14560,6 +14480,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BA1644BE-8582-47DF-8F3F-89F5A20E96EE}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9EAF8FBA-21F3-4051-8680-4ACAB3CDB416}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -14576,12 +14504,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BA1644BE-8582-47DF-8F3F-89F5A20E96EE}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>